--- a/methods_navigator/data/crosswalk.xlsx
+++ b/methods_navigator/data/crosswalk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Scott.Coffin\Documents\Claude\Projects\Quality Manuscript\methods_navigator\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E8516C-DE8F-4EBF-A132-5FF93D6DE466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{035FDAA5-11AE-4A89-B65F-B055D5CB6F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="Reviewer" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Crosswalk Table'!$A$2:$BB$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Crosswalk Table'!$A$2:$BB$187</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2593" uniqueCount="1415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2639" uniqueCount="1438">
   <si>
     <t>Reviewer Name</t>
   </si>
@@ -4487,7 +4487,76 @@
     <t>Database compiling 38 publications and 2 reports and web dashboard.</t>
   </si>
   <si>
-    <t>Alindayu et al. (2023)</t>
+    <t>OECD, 2026</t>
+  </si>
+  <si>
+    <t>Alindayu et al., 2023</t>
+  </si>
+  <si>
+    <t>Nanoplastics: reference and test materials production and characterisation, environmental fate and toxicity testing methods, report of an OECD state-of-the-art workshop.</t>
+  </si>
+  <si>
+    <t>https://one.oecd.org/document/ENV/CBC/MONO(2026)3/en/pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Since its establishment by an OECD Council Decision in 1971, the OECD Chemicals Programme, under the remit of the OECD Chemicals and Biotechnology Committee (hereafter CBC), has played a central role in advancing global chemical safety and biosafety. The core work of OECD Chemicals Programme includes developing standardized testing guidelines for chemical safety, fostering mutual acceptance of data, harmonizing risk assessment methodologies to protect both human health and the environment, and promoting efficient, cost-effective, and environmentally protective chemical management across member countries.  In November 2024, the CBC discussed the issue of nanoplastics present in the environment. It was agreed to organise a workshop to better understand the state-of-the-art research, any existing risk assessment activities and identify any potential regulatory needs. To support the organisation, an ad hoc steering group was launched, comprising experts in the field from industry, research and government agencies. The workshop was held on 12- 14 November 2025 at the OECD and was attended by 121 participants from academic research, national environmental research institutes, metrology organisations, national standardisation bodies, industry and animal welfare organisations. A total of 28 presentations were delivered to participants, with opportunities for questions and answers, and panel discussions addressing the following topics: • current landscape on international, regional and national activities on safety testing of nanoplastics,  • ongoing research on test methods for production characterisation of reference and test materials, • analytical methodologies and measurement challenges, and  • weathering and physical/chemical transformation techniques for environmentally relevant material Discussion on a definition of nanoplastics was not included in the workshop agenda, as the properties of reference and test materials—as well as the choice of testing methods—are highly dependent on the specific context and objectives of a given study. In this context, establishing a single global definition for nanoplastics, including precise size ranges and shapes, was considered outside the scope of the workshop. Workshop Overview  The workshop was opened by Bob Diderich, Head of Environment, Health and Safety Division at OECD. He explained that this workshop was organised following a recommendation from the CBC to scope the issue of toxicity and stability of fragmented nanoplastics and to better understand how the OECD can contribute to further harmonisation of tools and methods for their safety testing. This was followed by opening remarks from Jung-Kwan Seo, Director of Environmental Risk Division at National Institute of Environmental Research (NIER), Korea. Mr Seo highlighted that Korea has several research institutes addressing the potential hazards of nanoplastics to human health and environment. As such, they saw an Unclassified 10  ENV/CBC/MONO(2026)3 opportunity to support the workshop as a platform for sharing knowledge and experience, laying the foundation for strong international cooperation to mitigate issues related to nanoplastics. The workshop agenda was divided in six sessions held over three days (see Annex B for the Workshop Agenda). The topics addressed were as follows: Setting the Scene. This session featured three keynote presentations that provided a high-level overview of nanoplastics testing. Topics ranged from the processes and challenges associated with generating reference materials to the applicability of currently available OECD Test Guidelines to micro- and nanoplastics.  Standardization and international coordination for safety testing of nanoplastics. This was a panel discussion on efforts towards standardisation and international coordination for the safety testing of nanoplastics. The panel included three representatives from validation bodies and research consortia working on nanoplastics, as well as one representative from industry, who shared their perspectives on current activities and future needs.  Production and characterization of Reference Materials and Test Materials included presentations covering a range of particle generation methods representing both top-down and bottom-up approaches. The presentations and follow-up questions discussed the respective advantages of these production methods, their limitations and technical challenges. Analytical Methodologies and Measurement Challenges which highlighted issues associated with detecting and characterizing nanoplastics, arising from their small size, low concentrations, polymeric nature, and the complexity of surrounding matrices such as soil and biological tissues. Environmental Relevance &amp; Fate: Weathering and Physical/Chemical Transformation Techniques addressed different weathering techniques used to prepare environmentally relevant nanoplastics samples, with a focus on exposure routes (e.g., airborne) and release mechanisms (e.g., mechanical wear). Challenges in steps towards risk assessment framework for safety testing of nanoplastics was a panel session dedicated to discussions on existing risk assessment frameworks and on how tools and resources from nanomaterials risk assessment could be applied to nanoplastics. </t>
+  </si>
+  <si>
+    <t>Expert-documented current landscape on international, regional, and national activities on safety testing of nanoplastics; ongoing research on test methods for production characterisation of reference and test materials, analytical methodologies and measurement challenges; and weathering and physical/chemical transformation techniques for environmentally relevant material</t>
+  </si>
+  <si>
+    <t>Report detailing workshop regarding nanoplastics and state of science across toxicology, risk assesment, monitoring, and more.</t>
+  </si>
+  <si>
+    <t>CUSP, 2025</t>
+  </si>
+  <si>
+    <t>CUSP Research Roadmap 2026-2032: Informing and advising on the state of the art, gaps, and future needs in micro- and nanoplastic and health research in Europe</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5281/zenodo.17467125</t>
+  </si>
+  <si>
+    <t>Research roadmap from five EU H2020 projects (AURORA, IMPTOX, PlasticHeal, PlasticsFatE, POLYRISK) within the CUSP cluster. Identifies 22 priority research needs across five transversal themes: analytical methods and representative materials, exposure assessment, hazard assessment, risk assessment frameworks, and mitigation measures. Grouped by timeframe (immediate 0-2 yrs, mid 2-5 yrs, long-term &gt;5 yrs). DOI: 10.5281/zenodo.17467125. Zenodo. Presented at OECD nanoplastics workshop Nov 2025 (OECD 2026, ENV/CBC/MONO(2026)3).</t>
+  </si>
+  <si>
+    <t>Human health risk assessment of MNPs</t>
+  </si>
+  <si>
+    <t>Published 2025</t>
+  </si>
+  <si>
+    <t>Micro- and nanoplastics (MNPs); no specific size bounds defined</t>
+  </si>
+  <si>
+    <t>22 priority research needs; immediate, mid-term, and long-term research priorities; analytical methods gaps; exposure assessment gaps; hazard assessment gaps; risk assessment framework needs; mitigation measures</t>
+  </si>
+  <si>
+    <t>Micro- and nanoplastics (MNPs) have been detected in air, food, water, and in human blood, lungs, and placenta. Emerging evidence shows that these particles can cause inflammation, oxidative stress, and immune disturbances in cell-based or whole animal tests. Yet, significant knowledge gaps remain that hinder the reliable risk assessment of MNPs for humans, particularly regarding the health effects of long-term, low-level exposure and the risks for vulnerable groups such as children, pregnant women, and workers. The CUSP Research Roadmap 2026-2032 was developed by five Horizon 2020 projects (AURORA, IMPTOX, PlasticHeal, PlasticsFatE, POLYRISK) dedicated to researching the human health impacts of MNPs. It lays out the critical knowledge gaps and enabling of evidence-based action across 22 priority research needs grouped by timeframe. The CUSP Roadmap is a blueprint for action. It sets clear priorities for research, policy, and outreach, and provides the evidence base needed to guide regulation and innovation. It identifies the need for policymakers, scientists, and industry to work together strategically to reduce risks, accelerate the transition toward safer and more sustainable alternatives, and ultimately protect public health from the harms caused by MNPs.</t>
+  </si>
+  <si>
+    <t>Haase et al., 2026</t>
+  </si>
+  <si>
+    <t>Oral exposure to micro- and nanoplastics: Developing a modular and flexible risk assessment framework for human health</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.fct.2026.116041</t>
+  </si>
+  <si>
+    <t>POLYRISK oral exposure RA framework; companion to Vogel et al. 2024 (Row 19, inhalation focus). Three-step modular approach: (1) physicochemical characterization, (2) intestinal crossing assessment, (3) hazard assessment testing. Relies on IATAs, AOPs, and NAMs. Food Chem Toxicol 212:116041. PMID 41775312. Presented at OECD nanoplastics workshop Nov 2025 (OECD 2026, ENV/CBC/MONO(2026)3).</t>
+  </si>
+  <si>
+    <t>Human health oral exposure RA</t>
+  </si>
+  <si>
+    <t>Published 2026</t>
+  </si>
+  <si>
+    <t>Risk assessment framework steps; physicochemical characterization criteria; intestinal crossing assessment; hazard assessment testing modules; IATA integration; AOP integration; NAM-based testing strategies</t>
+  </si>
+  <si>
+    <t>Efficient strategies for the human health risk assessment of micro- and nanoplastics (MNPs) are urgently needed to address the complexity and diversity of these materials. Here, we propose a risk assessment framework for MNPs following the oral route of exposure. The framework is based on a flexible and modular approach, drawing on modern concepts in risk assessment, such as Integrated Approaches to Testing and Assessment (IATAs) or Adverse Outcome Pathways (AOPs), and substantially relies on New Approach Methodologies (NAMs). The framework is structured into three different main steps: i) basic physicochemical characterization of testing materials, ii) intestinal crossing, iii) hazard assessment testing. Each step of the framework is supported by scientifically sound methods, enabling a mechanistic and hypothesis-driven risk assessment of MNPs.</t>
   </si>
 </sst>
 </file>
@@ -5284,38 +5353,23 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="3" fontId="8" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -5338,15 +5392,30 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5866,8 +5935,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D7F74609-08FF-44E4-8D38-7B6CD8B94E02}" name="Table2" displayName="Table2" ref="A2:BB184" totalsRowShown="0" headerRowBorderDxfId="51">
-  <autoFilter ref="A2:BB184" xr:uid="{D7F74609-08FF-44E4-8D38-7B6CD8B94E02}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D7F74609-08FF-44E4-8D38-7B6CD8B94E02}" name="Table2" displayName="Table2" ref="A2:BB187" totalsRowShown="0" headerRowBorderDxfId="51">
+  <autoFilter ref="A2:BB187" xr:uid="{D7F74609-08FF-44E4-8D38-7B6CD8B94E02}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:BB176">
     <sortCondition ref="A2:A176"/>
   </sortState>
@@ -6264,75 +6333,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="66.599999999999994" hidden="1" customHeight="1">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="105" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="94" t="s">
+      <c r="B1" s="106"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="108" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="93"/>
-      <c r="N1" s="96" t="s">
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="110" t="s">
         <v>38</v>
       </c>
       <c r="O1" s="97"/>
       <c r="P1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="Q1" s="98" t="s">
+      <c r="Q1" s="111" t="s">
         <v>40</v>
       </c>
-      <c r="R1" s="92"/>
-      <c r="S1" s="92"/>
-      <c r="T1" s="92"/>
-      <c r="U1" s="92"/>
-      <c r="V1" s="92"/>
-      <c r="W1" s="92"/>
-      <c r="X1" s="92"/>
-      <c r="Y1" s="92"/>
-      <c r="Z1" s="92"/>
-      <c r="AA1" s="92"/>
-      <c r="AB1" s="92"/>
-      <c r="AC1" s="92"/>
+      <c r="R1" s="96"/>
+      <c r="S1" s="96"/>
+      <c r="T1" s="96"/>
+      <c r="U1" s="96"/>
+      <c r="V1" s="96"/>
+      <c r="W1" s="96"/>
+      <c r="X1" s="96"/>
+      <c r="Y1" s="96"/>
+      <c r="Z1" s="96"/>
+      <c r="AA1" s="96"/>
+      <c r="AB1" s="96"/>
+      <c r="AC1" s="96"/>
       <c r="AD1" s="97"/>
-      <c r="AE1" s="99" t="s">
+      <c r="AE1" s="112" t="s">
         <v>41</v>
       </c>
       <c r="AF1" s="97"/>
-      <c r="AG1" s="100" t="s">
+      <c r="AG1" s="95" t="s">
         <v>42</v>
       </c>
-      <c r="AH1" s="92"/>
-      <c r="AI1" s="92"/>
+      <c r="AH1" s="96"/>
+      <c r="AI1" s="96"/>
       <c r="AJ1" s="97"/>
       <c r="AK1" s="15"/>
       <c r="AL1" s="16" t="s">
         <v>43</v>
       </c>
       <c r="AM1" s="78"/>
-      <c r="AN1" s="101" t="s">
+      <c r="AN1" s="98" t="s">
         <v>44</v>
       </c>
       <c r="AO1" s="97"/>
-      <c r="AP1" s="102" t="s">
+      <c r="AP1" s="99" t="s">
         <v>45</v>
       </c>
       <c r="AQ1" s="97"/>
-      <c r="AR1" s="103" t="s">
+      <c r="AR1" s="100" t="s">
         <v>46</v>
       </c>
-      <c r="AS1" s="104"/>
-      <c r="AT1" s="104"/>
-      <c r="AU1" s="104"/>
+      <c r="AS1" s="101"/>
+      <c r="AT1" s="101"/>
+      <c r="AU1" s="101"/>
       <c r="AV1" s="17" t="s">
         <v>44</v>
       </c>
@@ -6341,11 +6410,11 @@
       </c>
       <c r="AX1" s="19"/>
       <c r="AY1" s="19"/>
-      <c r="AZ1" s="105" t="s">
+      <c r="AZ1" s="102" t="s">
         <v>48</v>
       </c>
-      <c r="BA1" s="106"/>
-      <c r="BB1" s="107"/>
+      <c r="BA1" s="103"/>
+      <c r="BB1" s="104"/>
     </row>
     <row r="2" spans="1:54" s="4" customFormat="1" ht="57.75" customHeight="1">
       <c r="A2" s="20" t="s">
@@ -23197,7 +23266,7 @@
       <c r="F178" s="68" t="s">
         <v>117</v>
       </c>
-      <c r="G178" s="108" t="s">
+      <c r="G178" s="90" t="s">
         <v>117</v>
       </c>
       <c r="H178" s="49" t="s">
@@ -23287,7 +23356,7 @@
       <c r="F179" s="68" t="s">
         <v>117</v>
       </c>
-      <c r="G179" s="108" t="s">
+      <c r="G179" s="90" t="s">
         <v>117</v>
       </c>
       <c r="H179" s="69" t="s">
@@ -23297,7 +23366,7 @@
         <v>105</v>
       </c>
       <c r="J179" s="81"/>
-      <c r="K179" s="109" t="s">
+      <c r="K179" s="91" t="s">
         <v>459</v>
       </c>
       <c r="L179" s="83"/>
@@ -23341,13 +23410,13 @@
       <c r="AT179" s="67"/>
       <c r="AU179" s="82"/>
       <c r="AV179" s="82"/>
-      <c r="AW179" s="110" t="s">
+      <c r="AW179" s="92" t="s">
         <v>1384</v>
       </c>
       <c r="AX179" s="83"/>
       <c r="AY179" s="83"/>
       <c r="AZ179" s="10"/>
-      <c r="BA179" s="110" t="s">
+      <c r="BA179" s="92" t="s">
         <v>1380</v>
       </c>
       <c r="BB179" s="10" t="s">
@@ -23373,7 +23442,7 @@
       <c r="F180" s="68" t="s">
         <v>117</v>
       </c>
-      <c r="G180" s="108" t="s">
+      <c r="G180" s="90" t="s">
         <v>117</v>
       </c>
       <c r="H180" s="69" t="s">
@@ -23383,7 +23452,7 @@
         <v>240</v>
       </c>
       <c r="J180" s="81"/>
-      <c r="K180" s="109" t="s">
+      <c r="K180" s="91" t="s">
         <v>907</v>
       </c>
       <c r="L180" s="83"/>
@@ -23429,7 +23498,7 @@
       <c r="AT180" s="67"/>
       <c r="AU180" s="82"/>
       <c r="AV180" s="82"/>
-      <c r="AW180" s="111" t="s">
+      <c r="AW180" s="93" t="s">
         <v>1385</v>
       </c>
       <c r="AX180" s="83"/>
@@ -23463,7 +23532,7 @@
       <c r="F181" s="68" t="s">
         <v>117</v>
       </c>
-      <c r="G181" s="108" t="s">
+      <c r="G181" s="90" t="s">
         <v>117</v>
       </c>
       <c r="H181" s="69" t="s">
@@ -23473,7 +23542,7 @@
         <v>105</v>
       </c>
       <c r="J181" s="81"/>
-      <c r="K181" s="109" t="s">
+      <c r="K181" s="91" t="s">
         <v>459</v>
       </c>
       <c r="L181" s="83"/>
@@ -23553,7 +23622,7 @@
       <c r="F182" s="68" t="s">
         <v>117</v>
       </c>
-      <c r="G182" s="108" t="s">
+      <c r="G182" s="90" t="s">
         <v>117</v>
       </c>
       <c r="H182" s="69" t="s">
@@ -23669,7 +23738,7 @@
       <c r="F183" s="68" t="s">
         <v>117</v>
       </c>
-      <c r="G183" s="108" t="s">
+      <c r="G183" s="90" t="s">
         <v>117</v>
       </c>
       <c r="H183" s="69" t="s">
@@ -23767,7 +23836,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="C184" s="82">
         <v>2023</v>
@@ -23775,13 +23844,13 @@
       <c r="D184" s="3" t="s">
         <v>1408</v>
       </c>
-      <c r="E184" s="112" t="s">
+      <c r="E184" s="94" t="s">
         <v>1409</v>
       </c>
       <c r="F184" s="68" t="s">
         <v>117</v>
       </c>
-      <c r="G184" s="108" t="s">
+      <c r="G184" s="90" t="s">
         <v>117</v>
       </c>
       <c r="H184" s="69" t="s">
@@ -23853,16 +23922,322 @@
       </c>
     </row>
     <row r="185" spans="1:54" ht="14.3" customHeight="1">
-      <c r="A185" s="70"/>
-      <c r="AW185" s="10"/>
+      <c r="A185" s="70">
+        <v>184</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C185" s="82">
+        <v>2026</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>1416</v>
+      </c>
+      <c r="E185" s="89" t="s">
+        <v>1417</v>
+      </c>
+      <c r="F185" s="68" t="s">
+        <v>102</v>
+      </c>
+      <c r="G185" s="39" t="s">
+        <v>230</v>
+      </c>
+      <c r="H185" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="I185" s="74" t="s">
+        <v>105</v>
+      </c>
+      <c r="J185" s="81"/>
+      <c r="K185" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="L185" s="53" t="s">
+        <v>232</v>
+      </c>
+      <c r="M185" s="85" t="s">
+        <v>186</v>
+      </c>
+      <c r="N185" s="82"/>
+      <c r="O185" s="82"/>
+      <c r="P185" s="82"/>
+      <c r="Q185" s="82"/>
+      <c r="R185" s="82"/>
+      <c r="S185" s="82"/>
+      <c r="T185" s="82"/>
+      <c r="U185" s="82"/>
+      <c r="V185" s="82"/>
+      <c r="W185" s="82"/>
+      <c r="X185" s="82"/>
+      <c r="Y185" s="82"/>
+      <c r="Z185" s="82"/>
+      <c r="AA185" s="82"/>
+      <c r="AB185" s="82"/>
+      <c r="AC185" s="82"/>
+      <c r="AD185" s="82"/>
+      <c r="AE185" s="82"/>
+      <c r="AF185" s="82"/>
+      <c r="AG185" s="82">
+        <v>2</v>
+      </c>
+      <c r="AH185" s="82"/>
+      <c r="AI185" s="82"/>
+      <c r="AJ185" s="82"/>
+      <c r="AK185" s="82"/>
+      <c r="AL185" s="82"/>
+      <c r="AM185" s="82">
+        <v>2</v>
+      </c>
+      <c r="AN185" s="82"/>
+      <c r="AO185" s="67"/>
+      <c r="AP185" s="82"/>
+      <c r="AQ185" s="82"/>
+      <c r="AR185" s="82"/>
+      <c r="AS185" s="82">
+        <v>2</v>
+      </c>
+      <c r="AT185" s="67"/>
+      <c r="AU185" s="82"/>
+      <c r="AV185" s="82">
+        <v>2</v>
+      </c>
+      <c r="AW185" s="10" t="s">
+        <v>1420</v>
+      </c>
+      <c r="AX185" s="83"/>
+      <c r="AY185" s="83"/>
+      <c r="AZ185" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="BA185" s="45" t="s">
+        <v>1419</v>
+      </c>
+      <c r="BB185" s="10" t="s">
+        <v>1418</v>
+      </c>
     </row>
     <row r="186" spans="1:54" ht="14.3" customHeight="1">
-      <c r="A186" s="70"/>
-      <c r="AW186" s="10"/>
+      <c r="A186" s="70">
+        <v>185</v>
+      </c>
+      <c r="B186" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C186">
+        <v>2025</v>
+      </c>
+      <c r="D186" t="s">
+        <v>1422</v>
+      </c>
+      <c r="E186" t="s">
+        <v>1423</v>
+      </c>
+      <c r="F186" s="68" t="s">
+        <v>102</v>
+      </c>
+      <c r="G186" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="H186" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="I186" s="75" t="s">
+        <v>167</v>
+      </c>
+      <c r="J186"/>
+      <c r="K186" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="L186" t="s">
+        <v>185</v>
+      </c>
+      <c r="M186" s="49" t="s">
+        <v>208</v>
+      </c>
+      <c r="N186">
+        <v>4</v>
+      </c>
+      <c r="O186">
+        <v>4</v>
+      </c>
+      <c r="P186"/>
+      <c r="Q186"/>
+      <c r="R186"/>
+      <c r="S186"/>
+      <c r="T186"/>
+      <c r="U186"/>
+      <c r="V186"/>
+      <c r="W186"/>
+      <c r="X186"/>
+      <c r="Y186"/>
+      <c r="Z186"/>
+      <c r="AA186">
+        <v>4</v>
+      </c>
+      <c r="AB186">
+        <v>4</v>
+      </c>
+      <c r="AC186">
+        <v>4</v>
+      </c>
+      <c r="AD186"/>
+      <c r="AE186"/>
+      <c r="AF186">
+        <v>4</v>
+      </c>
+      <c r="AG186"/>
+      <c r="AH186">
+        <v>4</v>
+      </c>
+      <c r="AI186"/>
+      <c r="AJ186">
+        <v>4</v>
+      </c>
+      <c r="AK186"/>
+      <c r="AL186">
+        <v>4</v>
+      </c>
+      <c r="AM186">
+        <v>4</v>
+      </c>
+      <c r="AN186"/>
+      <c r="AO186">
+        <v>4</v>
+      </c>
+      <c r="AP186">
+        <v>4</v>
+      </c>
+      <c r="AQ186">
+        <v>4</v>
+      </c>
+      <c r="AR186"/>
+      <c r="AS186">
+        <v>4</v>
+      </c>
+      <c r="AT186" t="s">
+        <v>1424</v>
+      </c>
+      <c r="AU186" t="s">
+        <v>1425</v>
+      </c>
+      <c r="AV186" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AW186" t="s">
+        <v>1427</v>
+      </c>
+      <c r="AX186" t="s">
+        <v>1428</v>
+      </c>
+      <c r="AY186" t="s">
+        <v>1429</v>
+      </c>
+      <c r="AZ186"/>
+      <c r="BA186"/>
     </row>
     <row r="187" spans="1:54" ht="14.3" customHeight="1">
-      <c r="A187" s="70"/>
-      <c r="AW187" s="10"/>
+      <c r="A187" s="70">
+        <v>186</v>
+      </c>
+      <c r="B187" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C187">
+        <v>2026</v>
+      </c>
+      <c r="D187" t="s">
+        <v>1431</v>
+      </c>
+      <c r="E187" t="s">
+        <v>1432</v>
+      </c>
+      <c r="F187" s="68" t="s">
+        <v>229</v>
+      </c>
+      <c r="G187" s="56" t="s">
+        <v>229</v>
+      </c>
+      <c r="H187" s="49" t="s">
+        <v>136</v>
+      </c>
+      <c r="I187" s="75" t="s">
+        <v>167</v>
+      </c>
+      <c r="J187"/>
+      <c r="K187" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="L187" t="s">
+        <v>185</v>
+      </c>
+      <c r="M187" s="49" t="s">
+        <v>208</v>
+      </c>
+      <c r="N187"/>
+      <c r="O187">
+        <v>4</v>
+      </c>
+      <c r="P187"/>
+      <c r="Q187"/>
+      <c r="R187"/>
+      <c r="S187"/>
+      <c r="T187"/>
+      <c r="U187"/>
+      <c r="V187"/>
+      <c r="W187"/>
+      <c r="X187"/>
+      <c r="Y187"/>
+      <c r="Z187"/>
+      <c r="AA187"/>
+      <c r="AB187">
+        <v>4</v>
+      </c>
+      <c r="AC187">
+        <v>4</v>
+      </c>
+      <c r="AD187"/>
+      <c r="AE187"/>
+      <c r="AF187"/>
+      <c r="AG187"/>
+      <c r="AH187"/>
+      <c r="AI187"/>
+      <c r="AJ187"/>
+      <c r="AK187"/>
+      <c r="AL187"/>
+      <c r="AM187"/>
+      <c r="AN187"/>
+      <c r="AO187"/>
+      <c r="AP187">
+        <v>4</v>
+      </c>
+      <c r="AQ187">
+        <v>4</v>
+      </c>
+      <c r="AR187"/>
+      <c r="AS187"/>
+      <c r="AT187">
+        <v>4</v>
+      </c>
+      <c r="AU187" t="s">
+        <v>1433</v>
+      </c>
+      <c r="AV187" t="s">
+        <v>1434</v>
+      </c>
+      <c r="AW187" t="s">
+        <v>1435</v>
+      </c>
+      <c r="AX187" t="s">
+        <v>1427</v>
+      </c>
+      <c r="AY187" t="s">
+        <v>1436</v>
+      </c>
+      <c r="AZ187" t="s">
+        <v>1437</v>
+      </c>
+      <c r="BA187"/>
     </row>
     <row r="188" spans="1:54" ht="14.3" customHeight="1">
       <c r="A188" s="70"/>
@@ -27187,16 +27562,16 @@
     <row r="1018" spans="1:49" ht="14.3" customHeight="1"/>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="F1:M1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="Q1:AD1"/>
+    <mergeCell ref="AE1:AF1"/>
     <mergeCell ref="AG1:AJ1"/>
     <mergeCell ref="AN1:AO1"/>
     <mergeCell ref="AP1:AQ1"/>
     <mergeCell ref="AR1:AU1"/>
     <mergeCell ref="AZ1:BB1"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="F1:M1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="Q1:AD1"/>
-    <mergeCell ref="AE1:AF1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E144" r:id="rId1" xr:uid="{A81C656A-0A99-4267-9649-0EEFD2B27222}"/>
@@ -27207,10 +27582,11 @@
     <hyperlink ref="E182" r:id="rId6" xr:uid="{D13A8F3D-BAB6-4E5A-89C7-E21C88CA3070}"/>
     <hyperlink ref="E183" r:id="rId7" xr:uid="{17CC5984-89BA-4B7E-8A6C-6BEE3DD0447E}"/>
     <hyperlink ref="E184" r:id="rId8" display="https://doi.org/10.1016/j.ocecoaman.2023.106771" xr:uid="{544CA07B-2E2A-4DBC-9CC6-55FE9D10C148}"/>
+    <hyperlink ref="E185" r:id="rId9" xr:uid="{9D95C0B9-0AF7-4B80-8A81-ABCD934682EF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId9"/>
+    <tablePart r:id="rId10"/>
   </tableParts>
 </worksheet>
 </file>

--- a/methods_navigator/data/crosswalk.xlsx
+++ b/methods_navigator/data/crosswalk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Scott.Coffin\Documents\Claude\Projects\Quality Manuscript\methods_navigator\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{035FDAA5-11AE-4A89-B65F-B055D5CB6F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9171BF-39F3-4BF7-8380-D118AF71E6A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4508,9 +4508,6 @@
     <t>Report detailing workshop regarding nanoplastics and state of science across toxicology, risk assesment, monitoring, and more.</t>
   </si>
   <si>
-    <t>CUSP, 2025</t>
-  </si>
-  <si>
     <t>CUSP Research Roadmap 2026-2032: Informing and advising on the state of the art, gaps, and future needs in micro- and nanoplastic and health research in Europe</t>
   </si>
   <si>
@@ -4535,9 +4532,6 @@
     <t>Micro- and nanoplastics (MNPs) have been detected in air, food, water, and in human blood, lungs, and placenta. Emerging evidence shows that these particles can cause inflammation, oxidative stress, and immune disturbances in cell-based or whole animal tests. Yet, significant knowledge gaps remain that hinder the reliable risk assessment of MNPs for humans, particularly regarding the health effects of long-term, low-level exposure and the risks for vulnerable groups such as children, pregnant women, and workers. The CUSP Research Roadmap 2026-2032 was developed by five Horizon 2020 projects (AURORA, IMPTOX, PlasticHeal, PlasticsFatE, POLYRISK) dedicated to researching the human health impacts of MNPs. It lays out the critical knowledge gaps and enabling of evidence-based action across 22 priority research needs grouped by timeframe. The CUSP Roadmap is a blueprint for action. It sets clear priorities for research, policy, and outreach, and provides the evidence base needed to guide regulation and innovation. It identifies the need for policymakers, scientists, and industry to work together strategically to reduce risks, accelerate the transition toward safer and more sustainable alternatives, and ultimately protect public health from the harms caused by MNPs.</t>
   </si>
   <si>
-    <t>Haase et al., 2026</t>
-  </si>
-  <si>
     <t>Oral exposure to micro- and nanoplastics: Developing a modular and flexible risk assessment framework for human health</t>
   </si>
   <si>
@@ -4557,6 +4551,12 @@
   </si>
   <si>
     <t>Efficient strategies for the human health risk assessment of micro- and nanoplastics (MNPs) are urgently needed to address the complexity and diversity of these materials. Here, we propose a risk assessment framework for MNPs following the oral route of exposure. The framework is based on a flexible and modular approach, drawing on modern concepts in risk assessment, such as Integrated Approaches to Testing and Assessment (IATAs) or Adverse Outcome Pathways (AOPs), and substantially relies on New Approach Methodologies (NAMs). The framework is structured into three different main steps: i) basic physicochemical characterization of testing materials, ii) intestinal crossing, iii) hazard assessment testing. Each step of the framework is supported by scientifically sound methods, enabling a mechanistic and hypothesis-driven risk assessment of MNPs.</t>
+  </si>
+  <si>
+    <t>Vogel et al., 2026</t>
+  </si>
+  <si>
+    <t>Muncke et al, 2025</t>
   </si>
 </sst>
 </file>
@@ -24022,16 +24022,16 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>1421</v>
+        <v>1437</v>
       </c>
       <c r="C186">
         <v>2025</v>
       </c>
       <c r="D186" t="s">
+        <v>1421</v>
+      </c>
+      <c r="E186" t="s">
         <v>1422</v>
-      </c>
-      <c r="E186" t="s">
-        <v>1423</v>
       </c>
       <c r="F186" s="68" t="s">
         <v>102</v>
@@ -24116,22 +24116,22 @@
         <v>4</v>
       </c>
       <c r="AT186" t="s">
+        <v>1423</v>
+      </c>
+      <c r="AU186" t="s">
         <v>1424</v>
       </c>
-      <c r="AU186" t="s">
+      <c r="AV186" t="s">
         <v>1425</v>
       </c>
-      <c r="AV186" t="s">
+      <c r="AW186" t="s">
         <v>1426</v>
       </c>
-      <c r="AW186" t="s">
+      <c r="AX186" t="s">
         <v>1427</v>
       </c>
-      <c r="AX186" t="s">
+      <c r="AY186" t="s">
         <v>1428</v>
-      </c>
-      <c r="AY186" t="s">
-        <v>1429</v>
       </c>
       <c r="AZ186"/>
       <c r="BA186"/>
@@ -24141,16 +24141,16 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>1430</v>
+        <v>1436</v>
       </c>
       <c r="C187">
         <v>2026</v>
       </c>
       <c r="D187" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="E187" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="F187" s="68" t="s">
         <v>229</v>
@@ -24220,22 +24220,22 @@
         <v>4</v>
       </c>
       <c r="AU187" t="s">
+        <v>1431</v>
+      </c>
+      <c r="AV187" t="s">
+        <v>1432</v>
+      </c>
+      <c r="AW187" t="s">
         <v>1433</v>
       </c>
-      <c r="AV187" t="s">
+      <c r="AX187" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AY187" t="s">
         <v>1434</v>
       </c>
-      <c r="AW187" t="s">
+      <c r="AZ187" t="s">
         <v>1435</v>
-      </c>
-      <c r="AX187" t="s">
-        <v>1427</v>
-      </c>
-      <c r="AY187" t="s">
-        <v>1436</v>
-      </c>
-      <c r="AZ187" t="s">
-        <v>1437</v>
       </c>
       <c r="BA187"/>
     </row>

--- a/methods_navigator/data/crosswalk.xlsx
+++ b/methods_navigator/data/crosswalk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Scott.Coffin\Documents\Claude\Projects\Quality Manuscript\methods_navigator\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E9171BF-39F3-4BF7-8380-D118AF71E6A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50F0CD4-6CB5-4170-8F58-0688FB067D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="Reviewer" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Crosswalk Table'!$A$2:$BB$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Crosswalk Table'!$A$2:$BB$188</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2639" uniqueCount="1438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2653" uniqueCount="1444">
   <si>
     <t>Reviewer Name</t>
   </si>
@@ -4557,6 +4557,24 @@
   </si>
   <si>
     <t>Muncke et al, 2025</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1021/acs.est.6c00693</t>
+  </si>
+  <si>
+    <t>Li et al., 2026</t>
+  </si>
+  <si>
+    <t>Preparation of Microplastics and Nanoplastics for Environmental Research</t>
+  </si>
+  <si>
+    <t>Comprehensive review offering critical guidance for selecting appropriate preparation methods tailored to specific experimental designs and conditions</t>
+  </si>
+  <si>
+    <t>Reproducible, convenient, and high-yield methods for the preparation of microplastics and nanoplastics (MNPs) are crucial for advancing the detection, degradation, and environmental and toxicological studies of these emerging contaminants. While commercial MNPs are commonly used, they suffer from limitations such as restricted polymer diversity, uniform spherical morphology, inadequate representation of environmental aging and weathering characteristics, and high costs. Conversely, environmentally collected MNPs, which hold significant relevance, often exhibit poor reproducibility, require extensive characterization, and are produced in low quantities. As a result, laboratory-based preparation of MNPs has gained traction. This review article examines various methods for MNP preparation, categorizing them into top-down and bottom-up approaches. Top-down methods involve the physical fragmentation of bulk plastics through mechanical processes such as grinding, cutting, milling, abrasion, or cryogenic treatment, resulting in particles that better mimic the irregular morphologies found in environmental plastics. In contrast, bottom-up methods encompass polymerization, precipitation, and self-assembly processes to produce MNPs with well-defined sizes, shapes, and surface chemistries. We discuss the advantages, limitations, and applicability of each method in detail, with a particular emphasis on the surface properties of the resulting MNPs. This comprehensive review offers critical guidance for selecting appropriate preparation methods tailored to specific experimental designs and conditions.</t>
+  </si>
+  <si>
+    <t>Review and guidance</t>
   </si>
 </sst>
 </file>
@@ -5090,7 +5108,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -5362,14 +5380,38 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="3" fontId="8" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -5392,36 +5434,29 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="52">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -5873,9 +5908,6 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -5935,66 +5967,66 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D7F74609-08FF-44E4-8D38-7B6CD8B94E02}" name="Table2" displayName="Table2" ref="A2:BB187" totalsRowShown="0" headerRowBorderDxfId="51">
-  <autoFilter ref="A2:BB187" xr:uid="{D7F74609-08FF-44E4-8D38-7B6CD8B94E02}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D7F74609-08FF-44E4-8D38-7B6CD8B94E02}" name="Table2" displayName="Table2" ref="A2:BB188" totalsRowShown="0" headerRowBorderDxfId="51">
+  <autoFilter ref="A2:BB188" xr:uid="{D7F74609-08FF-44E4-8D38-7B6CD8B94E02}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:BB176">
     <sortCondition ref="A2:A176"/>
   </sortState>
   <tableColumns count="54">
     <tableColumn id="1" xr3:uid="{157273E0-51BF-4198-AAA3-2216EFF6F18E}" name="#" dataDxfId="50"/>
     <tableColumn id="2" xr3:uid="{A8B1C8EE-F997-46EF-A198-05152546D1B5}" name="Short Citation" dataDxfId="49"/>
-    <tableColumn id="3" xr3:uid="{07F5FB6A-A650-41C8-A3B3-26567DEDC704}" name="Year" dataDxfId="48"/>
-    <tableColumn id="4" xr3:uid="{0831BE7B-82A3-4CA6-9FE4-C5DE13BF7499}" name="Full Title" dataDxfId="47"/>
-    <tableColumn id="5" xr3:uid="{8BDF9B71-F522-49EF-94E8-E0F244981500}" name="DOI/URL" dataDxfId="46"/>
-    <tableColumn id="6" xr3:uid="{19E5A9BF-1647-47BE-84D8-E72FF78D4F00}" name="Primary Domain" dataDxfId="45"/>
-    <tableColumn id="7" xr3:uid="{1365C634-3EE3-40D0-812F-4BA4FAED29E5}" name="Primary Focus" dataDxfId="44"/>
-    <tableColumn id="8" xr3:uid="{338122AB-5BD8-4866-A37E-3D39FA6670A2}" name="Document Type" dataDxfId="43"/>
-    <tableColumn id="9" xr3:uid="{27C9A60F-C709-4EA8-89A1-9E39AE07E9C1}" name="Priority_x000a_Tier" dataDxfId="42"/>
-    <tableColumn id="10" xr3:uid="{1D524DA9-0888-49F2-8229-DF236A082D36}" name="Instrumentation Tags" dataDxfId="41"/>
-    <tableColumn id="11" xr3:uid="{5C25CF41-F23E-4963-91C6-24C3E65B7436}" name="Matrix Tags" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{07F5FB6A-A650-41C8-A3B3-26567DEDC704}" name="Year" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{0831BE7B-82A3-4CA6-9FE4-C5DE13BF7499}" name="Full Title" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{8BDF9B71-F522-49EF-94E8-E0F244981500}" name="DOI/URL" dataDxfId="47"/>
+    <tableColumn id="6" xr3:uid="{19E5A9BF-1647-47BE-84D8-E72FF78D4F00}" name="Primary Domain" dataDxfId="46"/>
+    <tableColumn id="7" xr3:uid="{1365C634-3EE3-40D0-812F-4BA4FAED29E5}" name="Primary Focus" dataDxfId="45"/>
+    <tableColumn id="8" xr3:uid="{338122AB-5BD8-4866-A37E-3D39FA6670A2}" name="Document Type" dataDxfId="44"/>
+    <tableColumn id="9" xr3:uid="{27C9A60F-C709-4EA8-89A1-9E39AE07E9C1}" name="Priority_x000a_Tier" dataDxfId="43"/>
+    <tableColumn id="10" xr3:uid="{1D524DA9-0888-49F2-8229-DF236A082D36}" name="Instrumentation Tags" dataDxfId="42"/>
+    <tableColumn id="11" xr3:uid="{5C25CF41-F23E-4963-91C6-24C3E65B7436}" name="Matrix Tags" dataDxfId="41"/>
     <tableColumn id="12" xr3:uid="{FF901B25-2718-4138-805C-8F6455E23A05}" name="Particle/Polymer Type Tags"/>
-    <tableColumn id="13" xr3:uid="{CEDE63B6-1DE0-4F1C-819A-19776FC8DC6E}" name="Target Receptor(s)" dataDxfId="39"/>
-    <tableColumn id="14" xr3:uid="{9A4E571D-A1F6-40DC-B704-E1294F7DAB36}" name="Definitions &amp;_x000a_Terminology" dataDxfId="38"/>
-    <tableColumn id="15" xr3:uid="{941447EA-878B-4190-B298-856AC8347372}" name="Problem Formulation_x000a_/ Framework" dataDxfId="37"/>
-    <tableColumn id="16" xr3:uid="{CB178553-686B-4C5E-97E2-8A02E5FD0D55}" name="Sampling_x000a_(Field Methods)" dataDxfId="36"/>
-    <tableColumn id="17" xr3:uid="{228CC6E5-F85A-43D4-9C0D-E113F9ACA161}" name="Matrix:_x000a_Drinking Water" dataDxfId="35"/>
-    <tableColumn id="18" xr3:uid="{B123E62B-3AC0-435F-9145-4C8127CAA77C}" name="Matrix: Surface Water" dataDxfId="34"/>
-    <tableColumn id="19" xr3:uid="{CEF38C2B-2F06-4E78-A092-E2FEB97C9F52}" name="Matrix: Surface Water - Lacustrine" dataDxfId="33"/>
-    <tableColumn id="20" xr3:uid="{3694A582-64F6-4477-A9D8-06177956C242}" name="Matrix: Surface Water - Riverine" dataDxfId="32"/>
-    <tableColumn id="21" xr3:uid="{F583F8B6-3B8E-4B25-A98F-419E5647A5EA}" name="Matrix: Surface Water - Marine" dataDxfId="31"/>
-    <tableColumn id="22" xr3:uid="{85C0E723-D5C6-4324-94BB-D0F3DCA9B995}" name="Matrix:_x000a_Wastewater" dataDxfId="30"/>
-    <tableColumn id="23" xr3:uid="{8220585C-5CF1-41AF-919C-4C99A59721F7}" name="Matrix: Groundwater" dataDxfId="29"/>
-    <tableColumn id="24" xr3:uid="{FEBA89A1-F5D0-4F0D-B25F-6FB85D7243C0}" name="Matrix: Biosolids" dataDxfId="28"/>
-    <tableColumn id="25" xr3:uid="{09AB8842-0DF4-4F69-9168-1E1EDBACD5ED}" name="Matrix:_x000a_Sediment" dataDxfId="27"/>
-    <tableColumn id="26" xr3:uid="{0B7FDDE7-15ED-49F7-85D5-EC288FFD9ABF}" name="Matrix:_x000a_Soil" dataDxfId="26"/>
-    <tableColumn id="27" xr3:uid="{5C63260E-F930-45B8-BBDD-70838E6E43F5}" name="Matrix:_x000a_Biota/Tissue" dataDxfId="25"/>
-    <tableColumn id="28" xr3:uid="{DCD27DA6-354F-4360-8C09-BD78208BA02A}" name="Matrix:_x000a_Air/Atmos." dataDxfId="24"/>
-    <tableColumn id="29" xr3:uid="{4184C4AC-BEC3-404E-ACC5-AED032740DFF}" name="Matrix:_x000a_Food/Dietary" dataDxfId="23"/>
-    <tableColumn id="30" xr3:uid="{0E8CD545-AFE9-4376-8F44-48E6F9FC2936}" name="Matrix:_x000a_Human Tissue/_x000a_Biomonitor" dataDxfId="22"/>
-    <tableColumn id="31" xr3:uid="{4FAB3A2F-40D5-4FA8-BFC4-CB409107DB63}" name="Sample Processing_x000a_/ Extraction" dataDxfId="21"/>
-    <tableColumn id="32" xr3:uid="{5E7A3CB2-36D4-4594-BFB7-9F49BAA3A2D2}" name="Sub-sampling" dataDxfId="20"/>
-    <tableColumn id="33" xr3:uid="{1555478C-CD74-4F0E-9374-B5B012702DD9}" name="Analytical_x000a_Methods (General)" dataDxfId="19"/>
-    <tableColumn id="34" xr3:uid="{5E9715CD-9A76-4D03-9048-0AF3B32A2499}" name="FTIR / IR_x000a_Spectroscopy" dataDxfId="18"/>
-    <tableColumn id="35" xr3:uid="{6EF7B799-0FBF-4A00-9379-8FEADFA4E38A}" name="Raman_x000a_Spectroscopy" dataDxfId="17"/>
-    <tableColumn id="36" xr3:uid="{9C42805B-BA1D-45C3-9788-C9FB01D3D549}" name="Py-GC-MS" dataDxfId="16"/>
-    <tableColumn id="37" xr3:uid="{8DA2DD01-42A0-4C44-AB7F-B4754280832F}" name="Imaging" dataDxfId="15"/>
-    <tableColumn id="38" xr3:uid="{BB38F2B1-716D-48CA-A962-EA86DA3F849A}" name="Material Standards - materials" dataDxfId="14"/>
-    <tableColumn id="53" xr3:uid="{2E043EA4-F707-4069-9455-F0555C524C97}" name="Material Standards - protocol" dataDxfId="13"/>
-    <tableColumn id="39" xr3:uid="{9D69D833-46AC-4D69-A3FE-62512232C633}" name="Blanks &amp;_x000a_Contamination_x000a_Control" dataDxfId="12"/>
-    <tableColumn id="40" xr3:uid="{9628E9F5-3972-4FE0-9F02-83F8F9AB87B8}" name="Data Analysis_x000a_&amp; Statistics" dataDxfId="11"/>
-    <tableColumn id="41" xr3:uid="{E08A5C14-9082-4603-A2E5-0F190EA86465}" name="Reporting &amp;_x000a_Harmonization" dataDxfId="10"/>
-    <tableColumn id="42" xr3:uid="{15B782A9-BA11-42A8-8714-5859A51B9793}" name="Databases &amp;_x000a_Data Sharing" dataDxfId="9"/>
-    <tableColumn id="43" xr3:uid="{38DF8C33-36D2-431F-BB1C-E55F8D19DC14}" name="Toxicology:_x000a_Study Design &amp;_x000a_Dosimetry" dataDxfId="8"/>
-    <tableColumn id="44" xr3:uid="{D753897E-2232-42BB-B6A0-E9664869043F}" name="Toxicology:_x000a_Effects Testing_x000a_Methods" dataDxfId="7"/>
-    <tableColumn id="55" xr3:uid="{E25D3005-678F-4519-BBBF-F84B844C6386}" name="Toxicology: Reporting &amp; Harmonization" dataDxfId="6"/>
-    <tableColumn id="54" xr3:uid="{794AF906-9949-4D89-A079-01CE5E48D018}" name="Toxicology: Databases &amp; Data Sharing" dataDxfId="5"/>
-    <tableColumn id="46" xr3:uid="{3158ED12-9442-4B00-8CEC-E9D37D8F4E2D}" name="Risk_x000a_Assessment /_x000a_Risk Char." dataDxfId="4"/>
-    <tableColumn id="47" xr3:uid="{0FD00342-A9D9-478F-9383-D2F6B853A44D}" name="Key Notes" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{CEDE63B6-1DE0-4F1C-819A-19776FC8DC6E}" name="Target Receptor(s)" dataDxfId="40"/>
+    <tableColumn id="14" xr3:uid="{9A4E571D-A1F6-40DC-B704-E1294F7DAB36}" name="Definitions &amp;_x000a_Terminology" dataDxfId="39"/>
+    <tableColumn id="15" xr3:uid="{941447EA-878B-4190-B298-856AC8347372}" name="Problem Formulation_x000a_/ Framework" dataDxfId="38"/>
+    <tableColumn id="16" xr3:uid="{CB178553-686B-4C5E-97E2-8A02E5FD0D55}" name="Sampling_x000a_(Field Methods)" dataDxfId="37"/>
+    <tableColumn id="17" xr3:uid="{228CC6E5-F85A-43D4-9C0D-E113F9ACA161}" name="Matrix:_x000a_Drinking Water" dataDxfId="36"/>
+    <tableColumn id="18" xr3:uid="{B123E62B-3AC0-435F-9145-4C8127CAA77C}" name="Matrix: Surface Water" dataDxfId="35"/>
+    <tableColumn id="19" xr3:uid="{CEF38C2B-2F06-4E78-A092-E2FEB97C9F52}" name="Matrix: Surface Water - Lacustrine" dataDxfId="34"/>
+    <tableColumn id="20" xr3:uid="{3694A582-64F6-4477-A9D8-06177956C242}" name="Matrix: Surface Water - Riverine" dataDxfId="33"/>
+    <tableColumn id="21" xr3:uid="{F583F8B6-3B8E-4B25-A98F-419E5647A5EA}" name="Matrix: Surface Water - Marine" dataDxfId="32"/>
+    <tableColumn id="22" xr3:uid="{85C0E723-D5C6-4324-94BB-D0F3DCA9B995}" name="Matrix:_x000a_Wastewater" dataDxfId="31"/>
+    <tableColumn id="23" xr3:uid="{8220585C-5CF1-41AF-919C-4C99A59721F7}" name="Matrix: Groundwater" dataDxfId="30"/>
+    <tableColumn id="24" xr3:uid="{FEBA89A1-F5D0-4F0D-B25F-6FB85D7243C0}" name="Matrix: Biosolids" dataDxfId="29"/>
+    <tableColumn id="25" xr3:uid="{09AB8842-0DF4-4F69-9168-1E1EDBACD5ED}" name="Matrix:_x000a_Sediment" dataDxfId="28"/>
+    <tableColumn id="26" xr3:uid="{0B7FDDE7-15ED-49F7-85D5-EC288FFD9ABF}" name="Matrix:_x000a_Soil" dataDxfId="27"/>
+    <tableColumn id="27" xr3:uid="{5C63260E-F930-45B8-BBDD-70838E6E43F5}" name="Matrix:_x000a_Biota/Tissue" dataDxfId="26"/>
+    <tableColumn id="28" xr3:uid="{DCD27DA6-354F-4360-8C09-BD78208BA02A}" name="Matrix:_x000a_Air/Atmos." dataDxfId="25"/>
+    <tableColumn id="29" xr3:uid="{4184C4AC-BEC3-404E-ACC5-AED032740DFF}" name="Matrix:_x000a_Food/Dietary" dataDxfId="24"/>
+    <tableColumn id="30" xr3:uid="{0E8CD545-AFE9-4376-8F44-48E6F9FC2936}" name="Matrix:_x000a_Human Tissue/_x000a_Biomonitor" dataDxfId="23"/>
+    <tableColumn id="31" xr3:uid="{4FAB3A2F-40D5-4FA8-BFC4-CB409107DB63}" name="Sample Processing_x000a_/ Extraction" dataDxfId="22"/>
+    <tableColumn id="32" xr3:uid="{5E7A3CB2-36D4-4594-BFB7-9F49BAA3A2D2}" name="Sub-sampling" dataDxfId="21"/>
+    <tableColumn id="33" xr3:uid="{1555478C-CD74-4F0E-9374-B5B012702DD9}" name="Analytical_x000a_Methods (General)" dataDxfId="20"/>
+    <tableColumn id="34" xr3:uid="{5E9715CD-9A76-4D03-9048-0AF3B32A2499}" name="FTIR / IR_x000a_Spectroscopy" dataDxfId="19"/>
+    <tableColumn id="35" xr3:uid="{6EF7B799-0FBF-4A00-9379-8FEADFA4E38A}" name="Raman_x000a_Spectroscopy" dataDxfId="18"/>
+    <tableColumn id="36" xr3:uid="{9C42805B-BA1D-45C3-9788-C9FB01D3D549}" name="Py-GC-MS" dataDxfId="17"/>
+    <tableColumn id="37" xr3:uid="{8DA2DD01-42A0-4C44-AB7F-B4754280832F}" name="Imaging" dataDxfId="16"/>
+    <tableColumn id="38" xr3:uid="{BB38F2B1-716D-48CA-A962-EA86DA3F849A}" name="Material Standards - materials" dataDxfId="15"/>
+    <tableColumn id="53" xr3:uid="{2E043EA4-F707-4069-9455-F0555C524C97}" name="Material Standards - protocol" dataDxfId="14"/>
+    <tableColumn id="39" xr3:uid="{9D69D833-46AC-4D69-A3FE-62512232C633}" name="Blanks &amp;_x000a_Contamination_x000a_Control" dataDxfId="13"/>
+    <tableColumn id="40" xr3:uid="{9628E9F5-3972-4FE0-9F02-83F8F9AB87B8}" name="Data Analysis_x000a_&amp; Statistics" dataDxfId="12"/>
+    <tableColumn id="41" xr3:uid="{E08A5C14-9082-4603-A2E5-0F190EA86465}" name="Reporting &amp;_x000a_Harmonization" dataDxfId="11"/>
+    <tableColumn id="42" xr3:uid="{15B782A9-BA11-42A8-8714-5859A51B9793}" name="Databases &amp;_x000a_Data Sharing" dataDxfId="10"/>
+    <tableColumn id="43" xr3:uid="{38DF8C33-36D2-431F-BB1C-E55F8D19DC14}" name="Toxicology:_x000a_Study Design &amp;_x000a_Dosimetry" dataDxfId="9"/>
+    <tableColumn id="44" xr3:uid="{D753897E-2232-42BB-B6A0-E9664869043F}" name="Toxicology:_x000a_Effects Testing_x000a_Methods" dataDxfId="8"/>
+    <tableColumn id="55" xr3:uid="{E25D3005-678F-4519-BBBF-F84B844C6386}" name="Toxicology: Reporting &amp; Harmonization" dataDxfId="7"/>
+    <tableColumn id="54" xr3:uid="{794AF906-9949-4D89-A079-01CE5E48D018}" name="Toxicology: Databases &amp; Data Sharing" dataDxfId="6"/>
+    <tableColumn id="46" xr3:uid="{3158ED12-9442-4B00-8CEC-E9D37D8F4E2D}" name="Risk_x000a_Assessment /_x000a_Risk Char." dataDxfId="5"/>
+    <tableColumn id="47" xr3:uid="{0FD00342-A9D9-478F-9383-D2F6B853A44D}" name="Key Notes" dataDxfId="4"/>
     <tableColumn id="48" xr3:uid="{4BE1F33B-7E0D-4F32-B492-F28D43B48E54}" name="Scope"/>
     <tableColumn id="49" xr3:uid="{D2279340-23C3-4EE5-8570-F5244F0755EE}" name="Status"/>
-    <tableColumn id="50" xr3:uid="{81909305-108A-4B91-BCE6-89E889DE39A8}" name="Particle_x000a_Size Range" dataDxfId="2"/>
-    <tableColumn id="51" xr3:uid="{2AECE94C-1735-4B86-999E-F6C4105FFCFE}" name="Key Metrics /_x000a_Output" dataDxfId="1"/>
-    <tableColumn id="52" xr3:uid="{2DD3D9F5-1988-478B-BB45-CD54211D41B5}" name="Abstract" dataDxfId="0"/>
+    <tableColumn id="50" xr3:uid="{81909305-108A-4B91-BCE6-89E889DE39A8}" name="Particle_x000a_Size Range" dataDxfId="3"/>
+    <tableColumn id="51" xr3:uid="{2AECE94C-1735-4B86-999E-F6C4105FFCFE}" name="Key Metrics /_x000a_Output" dataDxfId="2"/>
+    <tableColumn id="52" xr3:uid="{2DD3D9F5-1988-478B-BB45-CD54211D41B5}" name="Abstract" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6333,75 +6365,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="66.599999999999994" hidden="1" customHeight="1">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="95" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="108" t="s">
+      <c r="B1" s="96"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="110" t="s">
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="100"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="101" t="s">
         <v>38</v>
       </c>
-      <c r="O1" s="97"/>
+      <c r="O1" s="102"/>
       <c r="P1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="Q1" s="111" t="s">
+      <c r="Q1" s="103" t="s">
         <v>40</v>
       </c>
-      <c r="R1" s="96"/>
-      <c r="S1" s="96"/>
-      <c r="T1" s="96"/>
-      <c r="U1" s="96"/>
-      <c r="V1" s="96"/>
-      <c r="W1" s="96"/>
-      <c r="X1" s="96"/>
-      <c r="Y1" s="96"/>
-      <c r="Z1" s="96"/>
-      <c r="AA1" s="96"/>
-      <c r="AB1" s="96"/>
-      <c r="AC1" s="96"/>
-      <c r="AD1" s="97"/>
-      <c r="AE1" s="112" t="s">
+      <c r="R1" s="97"/>
+      <c r="S1" s="97"/>
+      <c r="T1" s="97"/>
+      <c r="U1" s="97"/>
+      <c r="V1" s="97"/>
+      <c r="W1" s="97"/>
+      <c r="X1" s="97"/>
+      <c r="Y1" s="97"/>
+      <c r="Z1" s="97"/>
+      <c r="AA1" s="97"/>
+      <c r="AB1" s="97"/>
+      <c r="AC1" s="97"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="104" t="s">
         <v>41</v>
       </c>
-      <c r="AF1" s="97"/>
-      <c r="AG1" s="95" t="s">
+      <c r="AF1" s="102"/>
+      <c r="AG1" s="105" t="s">
         <v>42</v>
       </c>
-      <c r="AH1" s="96"/>
-      <c r="AI1" s="96"/>
-      <c r="AJ1" s="97"/>
+      <c r="AH1" s="97"/>
+      <c r="AI1" s="97"/>
+      <c r="AJ1" s="102"/>
       <c r="AK1" s="15"/>
       <c r="AL1" s="16" t="s">
         <v>43</v>
       </c>
       <c r="AM1" s="78"/>
-      <c r="AN1" s="98" t="s">
+      <c r="AN1" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="AO1" s="97"/>
-      <c r="AP1" s="99" t="s">
+      <c r="AO1" s="102"/>
+      <c r="AP1" s="107" t="s">
         <v>45</v>
       </c>
-      <c r="AQ1" s="97"/>
-      <c r="AR1" s="100" t="s">
+      <c r="AQ1" s="102"/>
+      <c r="AR1" s="108" t="s">
         <v>46</v>
       </c>
-      <c r="AS1" s="101"/>
-      <c r="AT1" s="101"/>
-      <c r="AU1" s="101"/>
+      <c r="AS1" s="109"/>
+      <c r="AT1" s="109"/>
+      <c r="AU1" s="109"/>
       <c r="AV1" s="17" t="s">
         <v>44</v>
       </c>
@@ -6410,11 +6442,11 @@
       </c>
       <c r="AX1" s="19"/>
       <c r="AY1" s="19"/>
-      <c r="AZ1" s="102" t="s">
+      <c r="AZ1" s="110" t="s">
         <v>48</v>
       </c>
-      <c r="BA1" s="103"/>
-      <c r="BB1" s="104"/>
+      <c r="BA1" s="111"/>
+      <c r="BB1" s="112"/>
     </row>
     <row r="2" spans="1:54" s="4" customFormat="1" ht="57.75" customHeight="1">
       <c r="A2" s="20" t="s">
@@ -6587,7 +6619,7 @@
       <c r="B3" s="37" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="36">
+      <c r="C3" s="113">
         <v>2009</v>
       </c>
       <c r="D3" s="37" t="s">
@@ -6685,7 +6717,7 @@
       <c r="B4" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="C4" s="36">
+      <c r="C4" s="113">
         <v>2013</v>
       </c>
       <c r="D4" s="37" t="s">
@@ -6793,7 +6825,7 @@
       <c r="B5" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="C5" s="36">
+      <c r="C5" s="113">
         <v>2015</v>
       </c>
       <c r="D5" s="37" t="s">
@@ -6897,7 +6929,7 @@
       <c r="B6" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="113">
         <v>2023</v>
       </c>
       <c r="D6" s="37" t="s">
@@ -6999,7 +7031,7 @@
       <c r="B7" s="37" t="s">
         <v>141</v>
       </c>
-      <c r="C7" s="36">
+      <c r="C7" s="113">
         <v>2025</v>
       </c>
       <c r="D7" s="37" t="s">
@@ -7103,7 +7135,7 @@
       <c r="B8" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="113">
         <v>2024</v>
       </c>
       <c r="D8" s="37" t="s">
@@ -7209,7 +7241,7 @@
       <c r="B9" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="113">
         <v>2023</v>
       </c>
       <c r="D9" s="37" t="s">
@@ -7315,7 +7347,7 @@
       <c r="B10" s="37" t="s">
         <v>163</v>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="113">
         <v>2021</v>
       </c>
       <c r="D10" s="37" t="s">
@@ -7409,7 +7441,7 @@
       <c r="B11" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="C11" s="36">
+      <c r="C11" s="113">
         <v>2025</v>
       </c>
       <c r="D11" s="37" t="s">
@@ -7505,7 +7537,7 @@
       <c r="B12" s="37" t="s">
         <v>180</v>
       </c>
-      <c r="C12" s="36">
+      <c r="C12" s="113">
         <v>2022</v>
       </c>
       <c r="D12" s="37" t="s">
@@ -7601,7 +7633,7 @@
       <c r="B13" s="37" t="s">
         <v>190</v>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="113">
         <v>2025</v>
       </c>
       <c r="D13" s="37" t="s">
@@ -7697,7 +7729,7 @@
       <c r="B14" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="113">
         <v>2025</v>
       </c>
       <c r="D14" s="37" t="s">
@@ -7789,7 +7821,7 @@
       <c r="B15" s="37" t="s">
         <v>202</v>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="113">
         <v>2020</v>
       </c>
       <c r="D15" s="37" t="s">
@@ -7883,7 +7915,7 @@
       <c r="B16" s="37" t="s">
         <v>212</v>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="113">
         <v>2011</v>
       </c>
       <c r="D16" s="37" t="s">
@@ -7971,7 +8003,7 @@
       <c r="B17" s="37" t="s">
         <v>218</v>
       </c>
-      <c r="C17" s="36">
+      <c r="C17" s="113">
         <v>2019</v>
       </c>
       <c r="D17" s="37" t="s">
@@ -8063,7 +8095,7 @@
       <c r="B18" s="37" t="s">
         <v>226</v>
       </c>
-      <c r="C18" s="36">
+      <c r="C18" s="113">
         <v>2017</v>
       </c>
       <c r="D18" s="37" t="s">
@@ -8163,7 +8195,7 @@
       <c r="B19" s="37" t="s">
         <v>237</v>
       </c>
-      <c r="C19" s="36">
+      <c r="C19" s="113">
         <v>2022</v>
       </c>
       <c r="D19" s="37" t="s">
@@ -8255,7 +8287,7 @@
       <c r="B20" s="37" t="s">
         <v>245</v>
       </c>
-      <c r="C20" s="36">
+      <c r="C20" s="113">
         <v>2023</v>
       </c>
       <c r="D20" s="37" t="s">
@@ -8351,7 +8383,7 @@
       <c r="B21" s="37" t="s">
         <v>251</v>
       </c>
-      <c r="C21" s="36">
+      <c r="C21" s="113">
         <v>2024</v>
       </c>
       <c r="D21" s="37" t="s">
@@ -8445,7 +8477,7 @@
       <c r="B22" s="37" t="s">
         <v>256</v>
       </c>
-      <c r="C22" s="36">
+      <c r="C22" s="113">
         <v>2024</v>
       </c>
       <c r="D22" s="37" t="s">
@@ -8531,7 +8563,7 @@
       <c r="B23" s="37" t="s">
         <v>261</v>
       </c>
-      <c r="C23" s="36">
+      <c r="C23" s="113">
         <v>2019</v>
       </c>
       <c r="D23" s="37" t="s">
@@ -8629,7 +8661,7 @@
       <c r="B24" s="37" t="s">
         <v>267</v>
       </c>
-      <c r="C24" s="36">
+      <c r="C24" s="113">
         <v>2022</v>
       </c>
       <c r="D24" s="37" t="s">
@@ -8723,7 +8755,7 @@
       <c r="B25" s="37" t="s">
         <v>275</v>
       </c>
-      <c r="C25" s="36">
+      <c r="C25" s="113">
         <v>2025</v>
       </c>
       <c r="D25" s="37" t="s">
@@ -8813,7 +8845,7 @@
       <c r="B26" s="37" t="s">
         <v>283</v>
       </c>
-      <c r="C26" s="36">
+      <c r="C26" s="113">
         <v>2021</v>
       </c>
       <c r="D26" s="37" t="s">
@@ -8909,7 +8941,7 @@
       <c r="B27" s="37" t="s">
         <v>290</v>
       </c>
-      <c r="C27" s="36">
+      <c r="C27" s="113">
         <v>2024</v>
       </c>
       <c r="D27" s="37" t="s">
@@ -8999,7 +9031,7 @@
       <c r="B28" s="37" t="s">
         <v>299</v>
       </c>
-      <c r="C28" s="36">
+      <c r="C28" s="113">
         <v>2020</v>
       </c>
       <c r="D28" s="37" t="s">
@@ -9095,7 +9127,7 @@
       <c r="B29" s="37" t="s">
         <v>305</v>
       </c>
-      <c r="C29" s="36">
+      <c r="C29" s="113">
         <v>2025</v>
       </c>
       <c r="D29" s="37" t="s">
@@ -9193,7 +9225,7 @@
       <c r="B30" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="C30" s="36">
+      <c r="C30" s="113">
         <v>2025</v>
       </c>
       <c r="D30" s="37" t="s">
@@ -9293,7 +9325,7 @@
       <c r="B31" s="37" t="s">
         <v>1350</v>
       </c>
-      <c r="C31" s="36">
+      <c r="C31" s="113">
         <v>2022</v>
       </c>
       <c r="D31" s="37" t="s">
@@ -9393,7 +9425,7 @@
       <c r="B32" s="37" t="s">
         <v>326</v>
       </c>
-      <c r="C32" s="36">
+      <c r="C32" s="113">
         <v>2024</v>
       </c>
       <c r="D32" s="37" t="s">
@@ -9483,7 +9515,7 @@
       <c r="B33" s="37" t="s">
         <v>333</v>
       </c>
-      <c r="C33" s="36">
+      <c r="C33" s="113">
         <v>2020</v>
       </c>
       <c r="D33" s="37" t="s">
@@ -9603,7 +9635,7 @@
       <c r="B34" s="37" t="s">
         <v>341</v>
       </c>
-      <c r="C34" s="36">
+      <c r="C34" s="113">
         <v>2020</v>
       </c>
       <c r="D34" s="37" t="s">
@@ -9721,7 +9753,7 @@
       <c r="B35" s="37" t="s">
         <v>348</v>
       </c>
-      <c r="C35" s="36">
+      <c r="C35" s="113">
         <v>2023</v>
       </c>
       <c r="D35" s="37" t="s">
@@ -9815,7 +9847,7 @@
       <c r="B36" s="37" t="s">
         <v>354</v>
       </c>
-      <c r="C36" s="36">
+      <c r="C36" s="113">
         <v>2024</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -9907,7 +9939,7 @@
       <c r="B37" s="37" t="s">
         <v>362</v>
       </c>
-      <c r="C37" s="36">
+      <c r="C37" s="113">
         <v>2019</v>
       </c>
       <c r="D37" s="37" t="s">
@@ -10015,7 +10047,7 @@
       <c r="B38" s="37" t="s">
         <v>369</v>
       </c>
-      <c r="C38" s="36">
+      <c r="C38" s="113">
         <v>2019</v>
       </c>
       <c r="D38" s="37" t="s">
@@ -10113,7 +10145,7 @@
       <c r="B39" s="37" t="s">
         <v>377</v>
       </c>
-      <c r="C39" s="36">
+      <c r="C39" s="113">
         <v>2026</v>
       </c>
       <c r="D39" s="37" t="s">
@@ -10211,7 +10243,7 @@
       <c r="B40" s="37" t="s">
         <v>385</v>
       </c>
-      <c r="C40" s="36">
+      <c r="C40" s="113">
         <v>2021</v>
       </c>
       <c r="D40" s="37" t="s">
@@ -10307,7 +10339,7 @@
       <c r="B41" s="37" t="s">
         <v>393</v>
       </c>
-      <c r="C41" s="36">
+      <c r="C41" s="113">
         <v>2020</v>
       </c>
       <c r="D41" s="37" t="s">
@@ -10407,7 +10439,7 @@
       <c r="B42" s="37" t="s">
         <v>399</v>
       </c>
-      <c r="C42" s="36">
+      <c r="C42" s="113">
         <v>2026</v>
       </c>
       <c r="D42" s="37" t="s">
@@ -10499,7 +10531,7 @@
       <c r="B43" s="37" t="s">
         <v>406</v>
       </c>
-      <c r="C43" s="36">
+      <c r="C43" s="113">
         <v>2022</v>
       </c>
       <c r="D43" s="37" t="s">
@@ -10597,7 +10629,7 @@
       <c r="B44" s="37" t="s">
         <v>413</v>
       </c>
-      <c r="C44" s="36">
+      <c r="C44" s="113">
         <v>2021</v>
       </c>
       <c r="D44" s="37" t="s">
@@ -10691,7 +10723,7 @@
       <c r="B45" s="37" t="s">
         <v>420</v>
       </c>
-      <c r="C45" s="36">
+      <c r="C45" s="113">
         <v>2022</v>
       </c>
       <c r="D45" s="37" t="s">
@@ -10783,7 +10815,7 @@
       <c r="B46" s="37" t="s">
         <v>377</v>
       </c>
-      <c r="C46" s="36">
+      <c r="C46" s="113">
         <v>2026</v>
       </c>
       <c r="D46" s="37" t="s">
@@ -10877,7 +10909,7 @@
       <c r="B47" s="37" t="s">
         <v>432</v>
       </c>
-      <c r="C47" s="36">
+      <c r="C47" s="113">
         <v>2022</v>
       </c>
       <c r="D47" s="37" t="s">
@@ -10969,7 +11001,7 @@
       <c r="B48" s="37" t="s">
         <v>439</v>
       </c>
-      <c r="C48" s="36">
+      <c r="C48" s="113">
         <v>2025</v>
       </c>
       <c r="D48" s="37" t="s">
@@ -11073,7 +11105,7 @@
       <c r="B49" s="37" t="s">
         <v>449</v>
       </c>
-      <c r="C49" s="36">
+      <c r="C49" s="113">
         <v>2022</v>
       </c>
       <c r="D49" s="37" t="s">
@@ -11167,7 +11199,7 @@
       <c r="B50" s="37" t="s">
         <v>456</v>
       </c>
-      <c r="C50" s="36">
+      <c r="C50" s="113">
         <v>2019</v>
       </c>
       <c r="D50" s="37" t="s">
@@ -11261,7 +11293,7 @@
       <c r="B51" s="37" t="s">
         <v>464</v>
       </c>
-      <c r="C51" s="36">
+      <c r="C51" s="113">
         <v>2023</v>
       </c>
       <c r="D51" s="37" t="s">
@@ -11355,7 +11387,7 @@
       <c r="B52" s="37" t="s">
         <v>473</v>
       </c>
-      <c r="C52" s="36">
+      <c r="C52" s="113">
         <v>2021</v>
       </c>
       <c r="D52" s="37" t="s">
@@ -11451,7 +11483,7 @@
       <c r="B53" s="37" t="s">
         <v>479</v>
       </c>
-      <c r="C53" s="36">
+      <c r="C53" s="113">
         <v>2023</v>
       </c>
       <c r="D53" s="37" t="s">
@@ -11561,7 +11593,7 @@
       <c r="B54" s="37" t="s">
         <v>486</v>
       </c>
-      <c r="C54" s="36">
+      <c r="C54" s="113">
         <v>2021</v>
       </c>
       <c r="D54" s="37" t="s">
@@ -11653,7 +11685,7 @@
       <c r="B55" s="37" t="s">
         <v>494</v>
       </c>
-      <c r="C55" s="36">
+      <c r="C55" s="113">
         <v>2021</v>
       </c>
       <c r="D55" s="37" t="s">
@@ -11747,7 +11779,7 @@
       <c r="B56" s="37" t="s">
         <v>501</v>
       </c>
-      <c r="C56" s="36">
+      <c r="C56" s="113">
         <v>2019</v>
       </c>
       <c r="D56" s="37" t="s">
@@ -11851,7 +11883,7 @@
       <c r="B57" s="37" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="36">
+      <c r="C57" s="113">
         <v>2015</v>
       </c>
       <c r="D57" s="37" t="s">
@@ -11947,7 +11979,7 @@
       <c r="B58" s="37" t="s">
         <v>514</v>
       </c>
-      <c r="C58" s="36">
+      <c r="C58" s="113">
         <v>2016</v>
       </c>
       <c r="D58" s="37" t="s">
@@ -12047,7 +12079,7 @@
       <c r="B59" s="37" t="s">
         <v>520</v>
       </c>
-      <c r="C59" s="36">
+      <c r="C59" s="113">
         <v>2019</v>
       </c>
       <c r="D59" s="37" t="s">
@@ -12137,7 +12169,7 @@
       <c r="B60" s="37" t="s">
         <v>525</v>
       </c>
-      <c r="C60" s="36">
+      <c r="C60" s="113">
         <v>2022</v>
       </c>
       <c r="D60" s="37" t="s">
@@ -12233,7 +12265,7 @@
       <c r="B61" s="37" t="s">
         <v>532</v>
       </c>
-      <c r="C61" s="36">
+      <c r="C61" s="113">
         <v>2015</v>
       </c>
       <c r="D61" s="37" t="s">
@@ -12327,7 +12359,7 @@
       <c r="B62" s="37" t="s">
         <v>540</v>
       </c>
-      <c r="C62" s="36">
+      <c r="C62" s="113">
         <v>2024</v>
       </c>
       <c r="D62" s="37" t="s">
@@ -12419,7 +12451,7 @@
       <c r="B63" s="37" t="s">
         <v>547</v>
       </c>
-      <c r="C63" s="36">
+      <c r="C63" s="113">
         <v>2021</v>
       </c>
       <c r="D63" s="37" t="s">
@@ -12513,7 +12545,7 @@
       <c r="B64" s="37" t="s">
         <v>554</v>
       </c>
-      <c r="C64" s="36">
+      <c r="C64" s="113">
         <v>2023</v>
       </c>
       <c r="D64" s="37" t="s">
@@ -12619,7 +12651,7 @@
       <c r="B65" s="37" t="s">
         <v>562</v>
       </c>
-      <c r="C65" s="36">
+      <c r="C65" s="113">
         <v>2020</v>
       </c>
       <c r="D65" s="37" t="s">
@@ -12715,7 +12747,7 @@
       <c r="B66" s="37" t="s">
         <v>569</v>
       </c>
-      <c r="C66" s="36">
+      <c r="C66" s="113">
         <v>2024</v>
       </c>
       <c r="D66" s="37" t="s">
@@ -12821,7 +12853,7 @@
       <c r="B67" s="37" t="s">
         <v>577</v>
       </c>
-      <c r="C67" s="36">
+      <c r="C67" s="113">
         <v>2023</v>
       </c>
       <c r="D67" s="37" t="s">
@@ -12929,7 +12961,7 @@
       <c r="B68" s="37" t="s">
         <v>583</v>
       </c>
-      <c r="C68" s="36">
+      <c r="C68" s="113">
         <v>2025</v>
       </c>
       <c r="D68" s="37" t="s">
@@ -13041,7 +13073,7 @@
       <c r="B69" s="37" t="s">
         <v>590</v>
       </c>
-      <c r="C69" s="36">
+      <c r="C69" s="113">
         <v>2026</v>
       </c>
       <c r="D69" s="37" t="s">
@@ -13139,7 +13171,7 @@
       <c r="B70" s="37" t="s">
         <v>597</v>
       </c>
-      <c r="C70" s="36">
+      <c r="C70" s="113">
         <v>2023</v>
       </c>
       <c r="D70" s="37" t="s">
@@ -13229,7 +13261,7 @@
       <c r="B71" s="58" t="s">
         <v>605</v>
       </c>
-      <c r="C71" s="59">
+      <c r="C71" s="114">
         <v>2026</v>
       </c>
       <c r="D71" s="58" t="s">
@@ -13319,7 +13351,7 @@
       <c r="B72" s="37" t="s">
         <v>613</v>
       </c>
-      <c r="C72" s="36">
+      <c r="C72" s="113">
         <v>2024</v>
       </c>
       <c r="D72" s="37" t="s">
@@ -13409,7 +13441,7 @@
       <c r="B73" s="37" t="s">
         <v>619</v>
       </c>
-      <c r="C73" s="36">
+      <c r="C73" s="113">
         <v>2024</v>
       </c>
       <c r="D73" s="37" t="s">
@@ -13501,7 +13533,7 @@
       <c r="B74" s="37" t="s">
         <v>627</v>
       </c>
-      <c r="C74" s="36">
+      <c r="C74" s="113">
         <v>2023</v>
       </c>
       <c r="D74" s="37" t="s">
@@ -13591,7 +13623,7 @@
       <c r="B75" s="37" t="s">
         <v>633</v>
       </c>
-      <c r="C75" s="36">
+      <c r="C75" s="113">
         <v>2017</v>
       </c>
       <c r="D75" s="37" t="s">
@@ -13687,7 +13719,7 @@
       <c r="B76" s="37" t="s">
         <v>641</v>
       </c>
-      <c r="C76" s="36">
+      <c r="C76" s="113">
         <v>2023</v>
       </c>
       <c r="D76" s="37" t="s">
@@ -13779,7 +13811,7 @@
       <c r="B77" s="37" t="s">
         <v>649</v>
       </c>
-      <c r="C77" s="36">
+      <c r="C77" s="113">
         <v>2023</v>
       </c>
       <c r="D77" s="37" t="s">
@@ -13873,7 +13905,7 @@
       <c r="B78" s="37" t="s">
         <v>656</v>
       </c>
-      <c r="C78" s="36">
+      <c r="C78" s="113">
         <v>2023</v>
       </c>
       <c r="D78" s="37" t="s">
@@ -13965,7 +13997,7 @@
       <c r="B79" s="37" t="s">
         <v>661</v>
       </c>
-      <c r="C79" s="36">
+      <c r="C79" s="113">
         <v>2025</v>
       </c>
       <c r="D79" s="37" t="s">
@@ -14067,7 +14099,7 @@
       <c r="B80" s="37" t="s">
         <v>666</v>
       </c>
-      <c r="C80" s="36">
+      <c r="C80" s="113">
         <v>2024</v>
       </c>
       <c r="D80" s="37" t="s">
@@ -14159,7 +14191,7 @@
       <c r="B81" s="37" t="s">
         <v>674</v>
       </c>
-      <c r="C81" s="36">
+      <c r="C81" s="113">
         <v>2019</v>
       </c>
       <c r="D81" s="37" t="s">
@@ -14251,7 +14283,7 @@
       <c r="B82" s="37" t="s">
         <v>682</v>
       </c>
-      <c r="C82" s="36">
+      <c r="C82" s="113">
         <v>2017</v>
       </c>
       <c r="D82" s="37" t="s">
@@ -14347,7 +14379,7 @@
       <c r="B83" s="58" t="s">
         <v>688</v>
       </c>
-      <c r="C83" s="59">
+      <c r="C83" s="114">
         <v>2026</v>
       </c>
       <c r="D83" s="58" t="s">
@@ -14437,7 +14469,7 @@
       <c r="B84" s="37" t="s">
         <v>694</v>
       </c>
-      <c r="C84" s="36">
+      <c r="C84" s="113">
         <v>2025</v>
       </c>
       <c r="D84" s="37" t="s">
@@ -14557,7 +14589,7 @@
       <c r="B85" s="37" t="s">
         <v>703</v>
       </c>
-      <c r="C85" s="36">
+      <c r="C85" s="113">
         <v>2023</v>
       </c>
       <c r="D85" s="37" t="s">
@@ -14647,7 +14679,7 @@
       <c r="B86" s="37" t="s">
         <v>709</v>
       </c>
-      <c r="C86" s="36">
+      <c r="C86" s="113">
         <v>2025</v>
       </c>
       <c r="D86" s="37" t="s">
@@ -14737,7 +14769,7 @@
       <c r="B87" s="37" t="s">
         <v>714</v>
       </c>
-      <c r="C87" s="36">
+      <c r="C87" s="113">
         <v>2024</v>
       </c>
       <c r="D87" s="37" t="s">
@@ -14831,7 +14863,7 @@
       <c r="B88" s="37" t="s">
         <v>722</v>
       </c>
-      <c r="C88" s="36">
+      <c r="C88" s="113">
         <v>2022</v>
       </c>
       <c r="D88" s="37" t="s">
@@ -14923,7 +14955,7 @@
       <c r="B89" s="37" t="s">
         <v>731</v>
       </c>
-      <c r="C89" s="36">
+      <c r="C89" s="113">
         <v>2019</v>
       </c>
       <c r="D89" s="37" t="s">
@@ -15023,7 +15055,7 @@
       <c r="B90" s="37" t="s">
         <v>739</v>
       </c>
-      <c r="C90" s="36">
+      <c r="C90" s="113">
         <v>2026</v>
       </c>
       <c r="D90" s="37" t="s">
@@ -15119,7 +15151,7 @@
       <c r="B91" s="58" t="s">
         <v>747</v>
       </c>
-      <c r="C91" s="59">
+      <c r="C91" s="114">
         <v>2026</v>
       </c>
       <c r="D91" s="61" t="s">
@@ -15213,7 +15245,7 @@
       <c r="B92" s="37" t="s">
         <v>753</v>
       </c>
-      <c r="C92" s="36">
+      <c r="C92" s="113">
         <v>2017</v>
       </c>
       <c r="D92" s="37" t="s">
@@ -15307,7 +15339,7 @@
       <c r="B93" s="37" t="s">
         <v>760</v>
       </c>
-      <c r="C93" s="36">
+      <c r="C93" s="113">
         <v>2022</v>
       </c>
       <c r="D93" s="37" t="s">
@@ -15407,7 +15439,7 @@
       <c r="B94" s="37" t="s">
         <v>767</v>
       </c>
-      <c r="C94" s="36">
+      <c r="C94" s="113">
         <v>2021</v>
       </c>
       <c r="D94" s="37" t="s">
@@ -15499,7 +15531,7 @@
       <c r="B95" s="37" t="s">
         <v>776</v>
       </c>
-      <c r="C95" s="36">
+      <c r="C95" s="113">
         <v>2023</v>
       </c>
       <c r="D95" s="37" t="s">
@@ -15587,7 +15619,7 @@
       <c r="B96" s="37" t="s">
         <v>783</v>
       </c>
-      <c r="C96" s="36">
+      <c r="C96" s="113">
         <v>2025</v>
       </c>
       <c r="D96" s="37" t="s">
@@ -15679,7 +15711,7 @@
       <c r="B97" s="37" t="s">
         <v>791</v>
       </c>
-      <c r="C97" s="36">
+      <c r="C97" s="113">
         <v>2025</v>
       </c>
       <c r="D97" s="37" t="s">
@@ -15779,7 +15811,7 @@
       <c r="B98" s="37" t="s">
         <v>799</v>
       </c>
-      <c r="C98" s="36">
+      <c r="C98" s="113">
         <v>2025</v>
       </c>
       <c r="D98" s="37" t="s">
@@ -15873,7 +15905,7 @@
       <c r="B99" s="37" t="s">
         <v>806</v>
       </c>
-      <c r="C99" s="36">
+      <c r="C99" s="113">
         <v>2020</v>
       </c>
       <c r="D99" s="37" t="s">
@@ -15971,7 +16003,7 @@
       <c r="B100" s="37" t="s">
         <v>814</v>
       </c>
-      <c r="C100" s="36">
+      <c r="C100" s="113">
         <v>2021</v>
       </c>
       <c r="D100" s="37" t="s">
@@ -16065,7 +16097,7 @@
       <c r="B101" s="37" t="s">
         <v>820</v>
       </c>
-      <c r="C101" s="36">
+      <c r="C101" s="113">
         <v>2022</v>
       </c>
       <c r="D101" s="37" t="s">
@@ -16161,7 +16193,7 @@
       <c r="B102" s="37" t="s">
         <v>827</v>
       </c>
-      <c r="C102" s="36">
+      <c r="C102" s="113">
         <v>2025</v>
       </c>
       <c r="D102" s="37" t="s">
@@ -16255,7 +16287,7 @@
       <c r="B103" s="37" t="s">
         <v>834</v>
       </c>
-      <c r="C103" s="36">
+      <c r="C103" s="113">
         <v>2025</v>
       </c>
       <c r="D103" s="37" t="s">
@@ -16353,7 +16385,7 @@
       <c r="B104" s="37" t="s">
         <v>841</v>
       </c>
-      <c r="C104" s="36">
+      <c r="C104" s="113">
         <v>2026</v>
       </c>
       <c r="D104" s="37" t="s">
@@ -16445,7 +16477,7 @@
       <c r="B105" s="37" t="s">
         <v>848</v>
       </c>
-      <c r="C105" s="36">
+      <c r="C105" s="113">
         <v>2021</v>
       </c>
       <c r="D105" s="37" t="s">
@@ -16535,7 +16567,7 @@
       <c r="B106" s="37" t="s">
         <v>856</v>
       </c>
-      <c r="C106" s="36">
+      <c r="C106" s="113">
         <v>2025</v>
       </c>
       <c r="D106" s="37" t="s">
@@ -16629,7 +16661,7 @@
       <c r="B107" s="37" t="s">
         <v>863</v>
       </c>
-      <c r="C107" s="36">
+      <c r="C107" s="113">
         <v>2022</v>
       </c>
       <c r="D107" s="37" t="s">
@@ -16723,7 +16755,7 @@
       <c r="B108" s="37" t="s">
         <v>870</v>
       </c>
-      <c r="C108" s="36">
+      <c r="C108" s="113">
         <v>2021</v>
       </c>
       <c r="D108" s="37" t="s">
@@ -16815,7 +16847,7 @@
       <c r="B109" s="37" t="s">
         <v>877</v>
       </c>
-      <c r="C109" s="36">
+      <c r="C109" s="113">
         <v>2021</v>
       </c>
       <c r="D109" s="37" t="s">
@@ -16923,7 +16955,7 @@
       <c r="B110" s="37" t="s">
         <v>884</v>
       </c>
-      <c r="C110" s="36">
+      <c r="C110" s="113">
         <v>2025</v>
       </c>
       <c r="D110" s="37" t="s">
@@ -17029,7 +17061,7 @@
       <c r="B111" s="37" t="s">
         <v>891</v>
       </c>
-      <c r="C111" s="36">
+      <c r="C111" s="113">
         <v>2022</v>
       </c>
       <c r="D111" s="37" t="s">
@@ -17125,7 +17157,7 @@
       <c r="B112" s="37" t="s">
         <v>898</v>
       </c>
-      <c r="C112" s="36">
+      <c r="C112" s="113">
         <v>2026</v>
       </c>
       <c r="D112" s="37" t="s">
@@ -17217,7 +17249,7 @@
       <c r="B113" s="37" t="s">
         <v>903</v>
       </c>
-      <c r="C113" s="36">
+      <c r="C113" s="113">
         <v>2022</v>
       </c>
       <c r="D113" s="37" t="s">
@@ -17319,7 +17351,7 @@
       <c r="B114" s="37" t="s">
         <v>912</v>
       </c>
-      <c r="C114" s="36">
+      <c r="C114" s="113">
         <v>2020</v>
       </c>
       <c r="D114" s="37" t="s">
@@ -17413,7 +17445,7 @@
       <c r="B115" s="37" t="s">
         <v>918</v>
       </c>
-      <c r="C115" s="36">
+      <c r="C115" s="113">
         <v>2019</v>
       </c>
       <c r="D115" s="37" t="s">
@@ -17503,7 +17535,7 @@
       <c r="B116" s="37" t="s">
         <v>924</v>
       </c>
-      <c r="C116" s="36">
+      <c r="C116" s="113">
         <v>2023</v>
       </c>
       <c r="D116" s="37" t="s">
@@ -17599,7 +17631,7 @@
       <c r="B117" s="37" t="s">
         <v>931</v>
       </c>
-      <c r="C117" s="36">
+      <c r="C117" s="113">
         <v>2025</v>
       </c>
       <c r="D117" s="37" t="s">
@@ -17723,7 +17755,7 @@
       <c r="B118" s="37" t="s">
         <v>938</v>
       </c>
-      <c r="C118" s="36">
+      <c r="C118" s="113">
         <v>2025</v>
       </c>
       <c r="D118" s="37" t="s">
@@ -17813,7 +17845,7 @@
       <c r="B119" s="37" t="s">
         <v>946</v>
       </c>
-      <c r="C119" s="36">
+      <c r="C119" s="113">
         <v>2014</v>
       </c>
       <c r="D119" s="37" t="s">
@@ -17903,7 +17935,7 @@
       <c r="B120" s="37" t="s">
         <v>953</v>
       </c>
-      <c r="C120" s="36">
+      <c r="C120" s="113">
         <v>2017</v>
       </c>
       <c r="D120" s="37" t="s">
@@ -17995,7 +18027,7 @@
       <c r="B121" s="37" t="s">
         <v>959</v>
       </c>
-      <c r="C121" s="36">
+      <c r="C121" s="113">
         <v>2020</v>
       </c>
       <c r="D121" s="37" t="s">
@@ -18083,7 +18115,7 @@
       <c r="B122" s="37" t="s">
         <v>965</v>
       </c>
-      <c r="C122" s="36">
+      <c r="C122" s="113">
         <v>2025</v>
       </c>
       <c r="D122" s="37" t="s">
@@ -18173,7 +18205,7 @@
       <c r="B123" s="37" t="s">
         <v>971</v>
       </c>
-      <c r="C123" s="36">
+      <c r="C123" s="113">
         <v>2021</v>
       </c>
       <c r="D123" s="37" t="s">
@@ -18267,7 +18299,7 @@
       <c r="B124" s="37" t="s">
         <v>979</v>
       </c>
-      <c r="C124" s="36">
+      <c r="C124" s="113">
         <v>2025</v>
       </c>
       <c r="D124" s="37" t="s">
@@ -18361,7 +18393,7 @@
       <c r="B125" s="37" t="s">
         <v>987</v>
       </c>
-      <c r="C125" s="36">
+      <c r="C125" s="113">
         <v>2007</v>
       </c>
       <c r="D125" s="37" t="s">
@@ -18451,7 +18483,7 @@
       <c r="B126" s="37" t="s">
         <v>994</v>
       </c>
-      <c r="C126" s="36">
+      <c r="C126" s="113">
         <v>2025</v>
       </c>
       <c r="D126" s="37" t="s">
@@ -18549,7 +18581,7 @@
       <c r="B127" s="37" t="s">
         <v>1001</v>
       </c>
-      <c r="C127" s="36">
+      <c r="C127" s="113">
         <v>2026</v>
       </c>
       <c r="D127" s="37" t="s">
@@ -18641,7 +18673,7 @@
       <c r="B128" s="37" t="s">
         <v>1010</v>
       </c>
-      <c r="C128" s="36">
+      <c r="C128" s="113">
         <v>2019</v>
       </c>
       <c r="D128" s="37" t="s">
@@ -18733,7 +18765,7 @@
       <c r="B129" s="37" t="s">
         <v>1014</v>
       </c>
-      <c r="C129" s="36">
+      <c r="C129" s="113">
         <v>2020</v>
       </c>
       <c r="D129" s="37" t="s">
@@ -18825,7 +18857,7 @@
       <c r="B130" s="37" t="s">
         <v>1021</v>
       </c>
-      <c r="C130" s="36">
+      <c r="C130" s="113">
         <v>2019</v>
       </c>
       <c r="D130" s="37" t="s">
@@ -18915,7 +18947,7 @@
       <c r="B131" s="37" t="s">
         <v>1028</v>
       </c>
-      <c r="C131" s="36">
+      <c r="C131" s="113">
         <v>2004</v>
       </c>
       <c r="D131" s="37" t="s">
@@ -19011,7 +19043,7 @@
       <c r="B132" s="37" t="s">
         <v>1032</v>
       </c>
-      <c r="C132" s="36">
+      <c r="C132" s="113">
         <v>2025</v>
       </c>
       <c r="D132" s="37" t="s">
@@ -19101,7 +19133,7 @@
       <c r="B133" s="37" t="s">
         <v>1040</v>
       </c>
-      <c r="C133" s="36">
+      <c r="C133" s="113">
         <v>2023</v>
       </c>
       <c r="D133" s="37" t="s">
@@ -19189,7 +19221,7 @@
       <c r="B134" s="37" t="s">
         <v>1047</v>
       </c>
-      <c r="C134" s="36">
+      <c r="C134" s="113">
         <v>2024</v>
       </c>
       <c r="D134" s="37" t="s">
@@ -19281,7 +19313,7 @@
       <c r="B135" s="37" t="s">
         <v>1055</v>
       </c>
-      <c r="C135" s="36">
+      <c r="C135" s="113">
         <v>2025</v>
       </c>
       <c r="D135" s="37" t="s">
@@ -19399,7 +19431,7 @@
       <c r="B136" s="37" t="s">
         <v>1063</v>
       </c>
-      <c r="C136" s="36">
+      <c r="C136" s="113">
         <v>2025</v>
       </c>
       <c r="D136" s="37" t="s">
@@ -19517,7 +19549,7 @@
       <c r="B137" s="37" t="s">
         <v>1070</v>
       </c>
-      <c r="C137" s="36">
+      <c r="C137" s="113">
         <v>2025</v>
       </c>
       <c r="D137" s="37" t="s">
@@ -19611,7 +19643,7 @@
       <c r="B138" s="37" t="s">
         <v>1079</v>
       </c>
-      <c r="C138" s="36">
+      <c r="C138" s="113">
         <v>2020</v>
       </c>
       <c r="D138" s="37" t="s">
@@ -19703,7 +19735,7 @@
       <c r="B139" s="37" t="s">
         <v>1086</v>
       </c>
-      <c r="C139" s="36">
+      <c r="C139" s="113">
         <v>2023</v>
       </c>
       <c r="D139" s="37" t="s">
@@ -19797,7 +19829,7 @@
       <c r="B140" s="37" t="s">
         <v>1096</v>
       </c>
-      <c r="C140" s="36">
+      <c r="C140" s="113">
         <v>2024</v>
       </c>
       <c r="D140" s="37" t="s">
@@ -19899,7 +19931,7 @@
       <c r="B141" s="37" t="s">
         <v>1103</v>
       </c>
-      <c r="C141" s="36">
+      <c r="C141" s="113">
         <v>2022</v>
       </c>
       <c r="D141" s="37" t="s">
@@ -20001,7 +20033,7 @@
       <c r="B142" s="37" t="s">
         <v>1110</v>
       </c>
-      <c r="C142" s="36">
+      <c r="C142" s="113">
         <v>2025</v>
       </c>
       <c r="D142" s="37" t="s">
@@ -20091,7 +20123,7 @@
       <c r="B143" s="37" t="s">
         <v>1115</v>
       </c>
-      <c r="C143" s="36">
+      <c r="C143" s="113">
         <v>2019</v>
       </c>
       <c r="D143" s="37" t="s">
@@ -20183,7 +20215,7 @@
       <c r="B144" s="37" t="s">
         <v>1120</v>
       </c>
-      <c r="C144" s="36">
+      <c r="C144" s="113">
         <v>2024</v>
       </c>
       <c r="D144" s="37" t="s">
@@ -20281,7 +20313,7 @@
       <c r="B145" s="37" t="s">
         <v>1126</v>
       </c>
-      <c r="C145" s="36">
+      <c r="C145" s="113">
         <v>2023</v>
       </c>
       <c r="D145" s="37" t="s">
@@ -20373,7 +20405,7 @@
       <c r="B146" s="37" t="s">
         <v>1131</v>
       </c>
-      <c r="C146" s="36">
+      <c r="C146" s="113">
         <v>2021</v>
       </c>
       <c r="D146" s="37" t="s">
@@ -20465,7 +20497,7 @@
       <c r="B147" s="37" t="s">
         <v>1137</v>
       </c>
-      <c r="C147" s="36">
+      <c r="C147" s="113">
         <v>2022</v>
       </c>
       <c r="D147" s="37" t="s">
@@ -20555,7 +20587,7 @@
       <c r="B148" s="37" t="s">
         <v>1143</v>
       </c>
-      <c r="C148" s="36">
+      <c r="C148" s="113">
         <v>2014</v>
       </c>
       <c r="D148" s="37" t="s">
@@ -20643,7 +20675,7 @@
       <c r="B149" s="37" t="s">
         <v>1150</v>
       </c>
-      <c r="C149" s="36">
+      <c r="C149" s="113">
         <v>2022</v>
       </c>
       <c r="D149" s="37" t="s">
@@ -20735,7 +20767,7 @@
       <c r="B150" s="37" t="s">
         <v>1156</v>
       </c>
-      <c r="C150" s="36">
+      <c r="C150" s="113">
         <v>2024</v>
       </c>
       <c r="D150" s="37" t="s">
@@ -20825,7 +20857,7 @@
       <c r="B151" s="37" t="s">
         <v>1162</v>
       </c>
-      <c r="C151" s="36">
+      <c r="C151" s="113">
         <v>2021</v>
       </c>
       <c r="D151" s="37" t="s">
@@ -20917,7 +20949,7 @@
       <c r="B152" s="37" t="s">
         <v>1169</v>
       </c>
-      <c r="C152" s="36">
+      <c r="C152" s="113">
         <v>2020</v>
       </c>
       <c r="D152" s="37" t="s">
@@ -21011,7 +21043,7 @@
       <c r="B153" s="37" t="s">
         <v>1176</v>
       </c>
-      <c r="C153" s="36">
+      <c r="C153" s="113">
         <v>2012</v>
       </c>
       <c r="D153" s="37" t="s">
@@ -21121,7 +21153,7 @@
       <c r="B154" s="37" t="s">
         <v>1184</v>
       </c>
-      <c r="C154" s="36">
+      <c r="C154" s="113">
         <v>2020</v>
       </c>
       <c r="D154" s="37" t="s">
@@ -21209,7 +21241,7 @@
       <c r="B155" s="37" t="s">
         <v>1190</v>
       </c>
-      <c r="C155" s="36">
+      <c r="C155" s="113">
         <v>2015</v>
       </c>
       <c r="D155" s="37" t="s">
@@ -21309,7 +21341,7 @@
       <c r="B156" s="37" t="s">
         <v>1198</v>
       </c>
-      <c r="C156" s="36">
+      <c r="C156" s="113">
         <v>2019</v>
       </c>
       <c r="D156" s="37" t="s">
@@ -21413,7 +21445,7 @@
       <c r="B157" s="37" t="s">
         <v>1204</v>
       </c>
-      <c r="C157" s="36">
+      <c r="C157" s="113">
         <v>2026</v>
       </c>
       <c r="D157" s="37" t="s">
@@ -21507,7 +21539,7 @@
       <c r="B158" s="37" t="s">
         <v>1212</v>
       </c>
-      <c r="C158" s="36">
+      <c r="C158" s="113">
         <v>2019</v>
       </c>
       <c r="D158" s="37" t="s">
@@ -21599,7 +21631,7 @@
       <c r="B159" s="37" t="s">
         <v>1219</v>
       </c>
-      <c r="C159" s="36">
+      <c r="C159" s="113">
         <v>2020</v>
       </c>
       <c r="D159" s="37" t="s">
@@ -21701,7 +21733,7 @@
       <c r="B160" s="37" t="s">
         <v>1226</v>
       </c>
-      <c r="C160" s="36">
+      <c r="C160" s="113">
         <v>2024</v>
       </c>
       <c r="D160" s="37" t="s">
@@ -21791,7 +21823,7 @@
       <c r="B161" s="37" t="s">
         <v>1233</v>
       </c>
-      <c r="C161" s="36">
+      <c r="C161" s="113">
         <v>2025</v>
       </c>
       <c r="D161" s="37" t="s">
@@ -21885,7 +21917,7 @@
       <c r="B162" s="37" t="s">
         <v>1240</v>
       </c>
-      <c r="C162" s="47">
+      <c r="C162" s="115">
         <v>2025</v>
       </c>
       <c r="D162" s="37" t="s">
@@ -21983,7 +22015,7 @@
       <c r="B163" s="37" t="s">
         <v>1246</v>
       </c>
-      <c r="C163" s="36">
+      <c r="C163" s="113">
         <v>2025</v>
       </c>
       <c r="D163" s="37" t="s">
@@ -22075,7 +22107,7 @@
       <c r="B164" s="37" t="s">
         <v>1252</v>
       </c>
-      <c r="C164" s="36">
+      <c r="C164" s="113">
         <v>2025</v>
       </c>
       <c r="D164" s="37" t="s">
@@ -22165,7 +22197,7 @@
       <c r="B165" s="37" t="s">
         <v>1260</v>
       </c>
-      <c r="C165" s="36">
+      <c r="C165" s="113">
         <v>2023</v>
       </c>
       <c r="D165" s="37" t="s">
@@ -22255,7 +22287,7 @@
       <c r="B166" s="37" t="s">
         <v>1266</v>
       </c>
-      <c r="C166" s="36">
+      <c r="C166" s="113">
         <v>1975</v>
       </c>
       <c r="D166" s="37" t="s">
@@ -22345,7 +22377,7 @@
       <c r="B167" s="37" t="s">
         <v>1273</v>
       </c>
-      <c r="C167" s="36">
+      <c r="C167" s="113">
         <v>2024</v>
       </c>
       <c r="D167" s="37" t="s">
@@ -22441,7 +22473,7 @@
       <c r="B168" s="63" t="s">
         <v>1276</v>
       </c>
-      <c r="C168" s="64">
+      <c r="C168" s="116">
         <v>2016</v>
       </c>
       <c r="D168" s="63" t="s">
@@ -22539,7 +22571,7 @@
       <c r="B169" s="63" t="s">
         <v>1286</v>
       </c>
-      <c r="C169" s="64">
+      <c r="C169" s="116">
         <v>2019</v>
       </c>
       <c r="D169" s="63" t="s">
@@ -22629,7 +22661,7 @@
       <c r="B170" s="63" t="s">
         <v>1293</v>
       </c>
-      <c r="C170" s="64">
+      <c r="C170" s="116">
         <v>2024</v>
       </c>
       <c r="D170" s="63" t="s">
@@ -22747,7 +22779,7 @@
       <c r="B171" s="37" t="s">
         <v>1298</v>
       </c>
-      <c r="C171" s="71">
+      <c r="C171" s="117">
         <v>2022</v>
       </c>
       <c r="D171" s="3" t="s">
@@ -22812,7 +22844,7 @@
       <c r="B172" s="3" t="s">
         <v>1303</v>
       </c>
-      <c r="C172" s="71">
+      <c r="C172" s="117">
         <v>2023</v>
       </c>
       <c r="D172" s="3" t="s">
@@ -22874,7 +22906,7 @@
       <c r="B173" s="3" t="s">
         <v>1309</v>
       </c>
-      <c r="C173" s="71">
+      <c r="C173" s="117">
         <v>2025</v>
       </c>
       <c r="D173" s="10" t="s">
@@ -22951,7 +22983,7 @@
       <c r="B174" s="3" t="s">
         <v>1314</v>
       </c>
-      <c r="C174" s="71">
+      <c r="C174" s="117">
         <v>2024</v>
       </c>
       <c r="D174" s="3" t="s">
@@ -23007,7 +23039,7 @@
       <c r="B175" s="3" t="s">
         <v>1319</v>
       </c>
-      <c r="C175" s="71">
+      <c r="C175" s="117">
         <v>2023</v>
       </c>
       <c r="D175" s="10" t="s">
@@ -23064,7 +23096,7 @@
       <c r="B176" s="37" t="s">
         <v>1351</v>
       </c>
-      <c r="C176" s="82">
+      <c r="C176" s="118">
         <v>2022</v>
       </c>
       <c r="D176" s="87" t="s">
@@ -23164,7 +23196,7 @@
       <c r="B177" s="3" t="s">
         <v>1364</v>
       </c>
-      <c r="C177" s="82">
+      <c r="C177" s="118">
         <v>2023</v>
       </c>
       <c r="D177" s="3" t="s">
@@ -23254,7 +23286,7 @@
       <c r="B178" s="3" t="s">
         <v>1372</v>
       </c>
-      <c r="C178" s="82">
+      <c r="C178" s="118">
         <v>2024</v>
       </c>
       <c r="D178" s="3" t="s">
@@ -23344,7 +23376,7 @@
       <c r="B179" s="3" t="s">
         <v>1376</v>
       </c>
-      <c r="C179" s="82">
+      <c r="C179" s="118">
         <v>2024</v>
       </c>
       <c r="D179" s="3" t="s">
@@ -23430,7 +23462,7 @@
       <c r="B180" s="3" t="s">
         <v>1381</v>
       </c>
-      <c r="C180" s="82">
+      <c r="C180" s="118">
         <v>2026</v>
       </c>
       <c r="D180" s="3" t="s">
@@ -23520,7 +23552,7 @@
       <c r="B181" s="3" t="s">
         <v>1391</v>
       </c>
-      <c r="C181" s="82">
+      <c r="C181" s="118">
         <v>2026</v>
       </c>
       <c r="D181" s="3" t="s">
@@ -23610,7 +23642,7 @@
       <c r="B182" s="3" t="s">
         <v>1396</v>
       </c>
-      <c r="C182" s="82">
+      <c r="C182" s="118">
         <v>2023</v>
       </c>
       <c r="D182" s="3" t="s">
@@ -23726,7 +23758,7 @@
       <c r="B183" s="3" t="s">
         <v>1403</v>
       </c>
-      <c r="C183" s="82">
+      <c r="C183" s="118">
         <v>2021</v>
       </c>
       <c r="D183" s="3" t="s">
@@ -23838,7 +23870,7 @@
       <c r="B184" s="3" t="s">
         <v>1415</v>
       </c>
-      <c r="C184" s="82">
+      <c r="C184" s="118">
         <v>2023</v>
       </c>
       <c r="D184" s="3" t="s">
@@ -23928,7 +23960,7 @@
       <c r="B185" s="3" t="s">
         <v>1414</v>
       </c>
-      <c r="C185" s="82">
+      <c r="C185" s="118">
         <v>2026</v>
       </c>
       <c r="D185" s="3" t="s">
@@ -24024,7 +24056,7 @@
       <c r="B186" t="s">
         <v>1437</v>
       </c>
-      <c r="C186">
+      <c r="C186" s="117">
         <v>2025</v>
       </c>
       <c r="D186" t="s">
@@ -24136,14 +24168,14 @@
       <c r="AZ186"/>
       <c r="BA186"/>
     </row>
-    <row r="187" spans="1:54" ht="14.3" customHeight="1">
+    <row r="187" spans="1:54" ht="27.2">
       <c r="A187" s="70">
         <v>186</v>
       </c>
       <c r="B187" t="s">
         <v>1436</v>
       </c>
-      <c r="C187">
+      <c r="C187" s="117">
         <v>2026</v>
       </c>
       <c r="D187" t="s">
@@ -24240,8 +24272,94 @@
       <c r="BA187"/>
     </row>
     <row r="188" spans="1:54" ht="14.3" customHeight="1">
-      <c r="A188" s="70"/>
-      <c r="AW188" s="10"/>
+      <c r="A188" s="70">
+        <v>187</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C188" s="118">
+        <v>2026</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>1440</v>
+      </c>
+      <c r="E188" s="94" t="s">
+        <v>1438</v>
+      </c>
+      <c r="F188" s="68" t="s">
+        <v>102</v>
+      </c>
+      <c r="G188" s="40" t="s">
+        <v>697</v>
+      </c>
+      <c r="H188" s="49" t="s">
+        <v>329</v>
+      </c>
+      <c r="I188" s="77" t="s">
+        <v>240</v>
+      </c>
+      <c r="J188" s="81"/>
+      <c r="K188" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="L188" t="s">
+        <v>185</v>
+      </c>
+      <c r="M188" s="85" t="s">
+        <v>186</v>
+      </c>
+      <c r="N188" s="82"/>
+      <c r="O188" s="82"/>
+      <c r="P188" s="82"/>
+      <c r="Q188" s="82"/>
+      <c r="R188" s="82"/>
+      <c r="S188" s="82"/>
+      <c r="T188" s="82"/>
+      <c r="U188" s="82"/>
+      <c r="V188" s="82"/>
+      <c r="W188" s="82"/>
+      <c r="X188" s="82"/>
+      <c r="Y188" s="82"/>
+      <c r="Z188" s="82"/>
+      <c r="AA188" s="82"/>
+      <c r="AB188" s="82"/>
+      <c r="AC188" s="82"/>
+      <c r="AD188" s="82"/>
+      <c r="AE188" s="82"/>
+      <c r="AF188" s="82"/>
+      <c r="AG188" s="82"/>
+      <c r="AH188" s="82"/>
+      <c r="AI188" s="82"/>
+      <c r="AJ188" s="82"/>
+      <c r="AK188" s="82"/>
+      <c r="AL188" s="82"/>
+      <c r="AM188" s="82">
+        <v>3</v>
+      </c>
+      <c r="AN188" s="82"/>
+      <c r="AO188" s="67"/>
+      <c r="AP188" s="82"/>
+      <c r="AQ188" s="82"/>
+      <c r="AR188" s="82"/>
+      <c r="AS188" s="82"/>
+      <c r="AT188" s="67"/>
+      <c r="AU188" s="82"/>
+      <c r="AV188" s="82"/>
+      <c r="AW188" s="10" t="s">
+        <v>1441</v>
+      </c>
+      <c r="AX188" s="83"/>
+      <c r="AY188" s="83"/>
+      <c r="AZ188" s="10" t="s">
+        <v>1393</v>
+      </c>
+      <c r="BA188" s="45" t="s">
+        <v>1443</v>
+      </c>
+      <c r="BB188" s="10" t="s">
+        <v>1442</v>
+      </c>
     </row>
     <row r="189" spans="1:54" ht="14.3" customHeight="1">
       <c r="A189" s="70"/>
@@ -27562,16 +27680,16 @@
     <row r="1018" spans="1:49" ht="14.3" customHeight="1"/>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AG1:AJ1"/>
+    <mergeCell ref="AN1:AO1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AR1:AU1"/>
+    <mergeCell ref="AZ1:BB1"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="F1:M1"/>
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="Q1:AD1"/>
     <mergeCell ref="AE1:AF1"/>
-    <mergeCell ref="AG1:AJ1"/>
-    <mergeCell ref="AN1:AO1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AR1:AU1"/>
-    <mergeCell ref="AZ1:BB1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E144" r:id="rId1" xr:uid="{A81C656A-0A99-4267-9649-0EEFD2B27222}"/>
@@ -27583,10 +27701,11 @@
     <hyperlink ref="E183" r:id="rId7" xr:uid="{17CC5984-89BA-4B7E-8A6C-6BEE3DD0447E}"/>
     <hyperlink ref="E184" r:id="rId8" display="https://doi.org/10.1016/j.ocecoaman.2023.106771" xr:uid="{544CA07B-2E2A-4DBC-9CC6-55FE9D10C148}"/>
     <hyperlink ref="E185" r:id="rId9" xr:uid="{9D95C0B9-0AF7-4B80-8A81-ABCD934682EF}"/>
+    <hyperlink ref="E188" r:id="rId10" tooltip="DOI URL" xr:uid="{71E22F72-0CF3-4154-834D-5AA603563583}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId10"/>
+    <tablePart r:id="rId11"/>
   </tableParts>
 </worksheet>
 </file>

--- a/methods_navigator/data/crosswalk.xlsx
+++ b/methods_navigator/data/crosswalk.xlsx
@@ -8,23 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Scott.Coffin\Documents\Claude\Projects\Quality Manuscript\methods_navigator\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50F0CD4-6CB5-4170-8F58-0688FB067D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F54853E3-F5AB-4777-BF53-063D8924D940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25974" yWindow="-4008" windowWidth="34995" windowHeight="19060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Crosswalk Table" sheetId="1" r:id="rId1"/>
     <sheet name="Reviewer" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Crosswalk Table'!$A$2:$BB$188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Crosswalk Table'!$A$2:$BB$189</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2653" uniqueCount="1444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2667" uniqueCount="1451">
   <si>
     <t>Reviewer Name</t>
   </si>
@@ -4575,6 +4575,27 @@
   </si>
   <si>
     <t>Review and guidance</t>
+  </si>
+  <si>
+    <t>Al-Zawaidah &amp; Waldschläger, 2026</t>
+  </si>
+  <si>
+    <t>A practical checklist for where, when, and what to measure - A systematic review of ten years of laboratory research on microplastic transport in rivers and transitional zones</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1186/s43591-026-00190-9</t>
+  </si>
+  <si>
+    <t>Freshwater, Marine Water</t>
+  </si>
+  <si>
+    <t>Microplastic pollution in freshwater is a global concern, yet field monitoring often lacks standardization, hindering data comparability and analysis. This systematic review bridges the gap between lab findings and field sampling by analyzing 173 peer-reviewed laboratory studies on freshwater systems, published in English and identified through Web of Science up to August 2024, to extract critical processes affecting microplastic transport and to provide recommendations on where, when, and what to sample in rivers and transitional zones. We highlight priority locations such as salinity gradients, biologically active zones, and hydrodynamically diverse areas. Temporal guidance includes the duration of hydrodynamic and biological processes, study objectives (transport vs. retention), and sudden environmental disturbances such as floods or algal bloom collapses. For particle characterization, we evaluate shape descriptors and recommend recording at least the three principal dimensions, as they can be translated into quantitative shape descriptors relevant for modelling. Finally, we present a practical checklist outlining essential measurements for microplastics, water, sediment, additional substances, and surrounding conditions. Incorporating these insights into future monitoring campaigns will improve the ecological relevance and interpretability of microplastic monitoring.</t>
+  </si>
+  <si>
+    <t>Guidance and checklist</t>
+  </si>
+  <si>
+    <t>Comprehensive review up to August 2024 with harmonized recommendations on where, when, and what to sample in rivers and transitional zones.</t>
   </si>
 </sst>
 </file>
@@ -5108,7 +5129,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -5380,38 +5401,17 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="3" fontId="8" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -5434,19 +5434,30 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="8" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -5454,9 +5465,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="52">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -5908,6 +5916,9 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -5967,66 +5978,66 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D7F74609-08FF-44E4-8D38-7B6CD8B94E02}" name="Table2" displayName="Table2" ref="A2:BB188" totalsRowShown="0" headerRowBorderDxfId="51">
-  <autoFilter ref="A2:BB188" xr:uid="{D7F74609-08FF-44E4-8D38-7B6CD8B94E02}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D7F74609-08FF-44E4-8D38-7B6CD8B94E02}" name="Table2" displayName="Table2" ref="A2:BB189" totalsRowShown="0" headerRowBorderDxfId="51">
+  <autoFilter ref="A2:BB189" xr:uid="{D7F74609-08FF-44E4-8D38-7B6CD8B94E02}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:BB176">
     <sortCondition ref="A2:A176"/>
   </sortState>
   <tableColumns count="54">
     <tableColumn id="1" xr3:uid="{157273E0-51BF-4198-AAA3-2216EFF6F18E}" name="#" dataDxfId="50"/>
     <tableColumn id="2" xr3:uid="{A8B1C8EE-F997-46EF-A198-05152546D1B5}" name="Short Citation" dataDxfId="49"/>
-    <tableColumn id="3" xr3:uid="{07F5FB6A-A650-41C8-A3B3-26567DEDC704}" name="Year" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{0831BE7B-82A3-4CA6-9FE4-C5DE13BF7499}" name="Full Title" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{8BDF9B71-F522-49EF-94E8-E0F244981500}" name="DOI/URL" dataDxfId="47"/>
-    <tableColumn id="6" xr3:uid="{19E5A9BF-1647-47BE-84D8-E72FF78D4F00}" name="Primary Domain" dataDxfId="46"/>
-    <tableColumn id="7" xr3:uid="{1365C634-3EE3-40D0-812F-4BA4FAED29E5}" name="Primary Focus" dataDxfId="45"/>
-    <tableColumn id="8" xr3:uid="{338122AB-5BD8-4866-A37E-3D39FA6670A2}" name="Document Type" dataDxfId="44"/>
-    <tableColumn id="9" xr3:uid="{27C9A60F-C709-4EA8-89A1-9E39AE07E9C1}" name="Priority_x000a_Tier" dataDxfId="43"/>
-    <tableColumn id="10" xr3:uid="{1D524DA9-0888-49F2-8229-DF236A082D36}" name="Instrumentation Tags" dataDxfId="42"/>
-    <tableColumn id="11" xr3:uid="{5C25CF41-F23E-4963-91C6-24C3E65B7436}" name="Matrix Tags" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{07F5FB6A-A650-41C8-A3B3-26567DEDC704}" name="Year" dataDxfId="48"/>
+    <tableColumn id="4" xr3:uid="{0831BE7B-82A3-4CA6-9FE4-C5DE13BF7499}" name="Full Title" dataDxfId="47"/>
+    <tableColumn id="5" xr3:uid="{8BDF9B71-F522-49EF-94E8-E0F244981500}" name="DOI/URL" dataDxfId="46"/>
+    <tableColumn id="6" xr3:uid="{19E5A9BF-1647-47BE-84D8-E72FF78D4F00}" name="Primary Domain" dataDxfId="45"/>
+    <tableColumn id="7" xr3:uid="{1365C634-3EE3-40D0-812F-4BA4FAED29E5}" name="Primary Focus" dataDxfId="44"/>
+    <tableColumn id="8" xr3:uid="{338122AB-5BD8-4866-A37E-3D39FA6670A2}" name="Document Type" dataDxfId="43"/>
+    <tableColumn id="9" xr3:uid="{27C9A60F-C709-4EA8-89A1-9E39AE07E9C1}" name="Priority_x000a_Tier" dataDxfId="42"/>
+    <tableColumn id="10" xr3:uid="{1D524DA9-0888-49F2-8229-DF236A082D36}" name="Instrumentation Tags" dataDxfId="41"/>
+    <tableColumn id="11" xr3:uid="{5C25CF41-F23E-4963-91C6-24C3E65B7436}" name="Matrix Tags" dataDxfId="40"/>
     <tableColumn id="12" xr3:uid="{FF901B25-2718-4138-805C-8F6455E23A05}" name="Particle/Polymer Type Tags"/>
-    <tableColumn id="13" xr3:uid="{CEDE63B6-1DE0-4F1C-819A-19776FC8DC6E}" name="Target Receptor(s)" dataDxfId="40"/>
-    <tableColumn id="14" xr3:uid="{9A4E571D-A1F6-40DC-B704-E1294F7DAB36}" name="Definitions &amp;_x000a_Terminology" dataDxfId="39"/>
-    <tableColumn id="15" xr3:uid="{941447EA-878B-4190-B298-856AC8347372}" name="Problem Formulation_x000a_/ Framework" dataDxfId="38"/>
-    <tableColumn id="16" xr3:uid="{CB178553-686B-4C5E-97E2-8A02E5FD0D55}" name="Sampling_x000a_(Field Methods)" dataDxfId="37"/>
-    <tableColumn id="17" xr3:uid="{228CC6E5-F85A-43D4-9C0D-E113F9ACA161}" name="Matrix:_x000a_Drinking Water" dataDxfId="36"/>
-    <tableColumn id="18" xr3:uid="{B123E62B-3AC0-435F-9145-4C8127CAA77C}" name="Matrix: Surface Water" dataDxfId="35"/>
-    <tableColumn id="19" xr3:uid="{CEF38C2B-2F06-4E78-A092-E2FEB97C9F52}" name="Matrix: Surface Water - Lacustrine" dataDxfId="34"/>
-    <tableColumn id="20" xr3:uid="{3694A582-64F6-4477-A9D8-06177956C242}" name="Matrix: Surface Water - Riverine" dataDxfId="33"/>
-    <tableColumn id="21" xr3:uid="{F583F8B6-3B8E-4B25-A98F-419E5647A5EA}" name="Matrix: Surface Water - Marine" dataDxfId="32"/>
-    <tableColumn id="22" xr3:uid="{85C0E723-D5C6-4324-94BB-D0F3DCA9B995}" name="Matrix:_x000a_Wastewater" dataDxfId="31"/>
-    <tableColumn id="23" xr3:uid="{8220585C-5CF1-41AF-919C-4C99A59721F7}" name="Matrix: Groundwater" dataDxfId="30"/>
-    <tableColumn id="24" xr3:uid="{FEBA89A1-F5D0-4F0D-B25F-6FB85D7243C0}" name="Matrix: Biosolids" dataDxfId="29"/>
-    <tableColumn id="25" xr3:uid="{09AB8842-0DF4-4F69-9168-1E1EDBACD5ED}" name="Matrix:_x000a_Sediment" dataDxfId="28"/>
-    <tableColumn id="26" xr3:uid="{0B7FDDE7-15ED-49F7-85D5-EC288FFD9ABF}" name="Matrix:_x000a_Soil" dataDxfId="27"/>
-    <tableColumn id="27" xr3:uid="{5C63260E-F930-45B8-BBDD-70838E6E43F5}" name="Matrix:_x000a_Biota/Tissue" dataDxfId="26"/>
-    <tableColumn id="28" xr3:uid="{DCD27DA6-354F-4360-8C09-BD78208BA02A}" name="Matrix:_x000a_Air/Atmos." dataDxfId="25"/>
-    <tableColumn id="29" xr3:uid="{4184C4AC-BEC3-404E-ACC5-AED032740DFF}" name="Matrix:_x000a_Food/Dietary" dataDxfId="24"/>
-    <tableColumn id="30" xr3:uid="{0E8CD545-AFE9-4376-8F44-48E6F9FC2936}" name="Matrix:_x000a_Human Tissue/_x000a_Biomonitor" dataDxfId="23"/>
-    <tableColumn id="31" xr3:uid="{4FAB3A2F-40D5-4FA8-BFC4-CB409107DB63}" name="Sample Processing_x000a_/ Extraction" dataDxfId="22"/>
-    <tableColumn id="32" xr3:uid="{5E7A3CB2-36D4-4594-BFB7-9F49BAA3A2D2}" name="Sub-sampling" dataDxfId="21"/>
-    <tableColumn id="33" xr3:uid="{1555478C-CD74-4F0E-9374-B5B012702DD9}" name="Analytical_x000a_Methods (General)" dataDxfId="20"/>
-    <tableColumn id="34" xr3:uid="{5E9715CD-9A76-4D03-9048-0AF3B32A2499}" name="FTIR / IR_x000a_Spectroscopy" dataDxfId="19"/>
-    <tableColumn id="35" xr3:uid="{6EF7B799-0FBF-4A00-9379-8FEADFA4E38A}" name="Raman_x000a_Spectroscopy" dataDxfId="18"/>
-    <tableColumn id="36" xr3:uid="{9C42805B-BA1D-45C3-9788-C9FB01D3D549}" name="Py-GC-MS" dataDxfId="17"/>
-    <tableColumn id="37" xr3:uid="{8DA2DD01-42A0-4C44-AB7F-B4754280832F}" name="Imaging" dataDxfId="16"/>
-    <tableColumn id="38" xr3:uid="{BB38F2B1-716D-48CA-A962-EA86DA3F849A}" name="Material Standards - materials" dataDxfId="15"/>
-    <tableColumn id="53" xr3:uid="{2E043EA4-F707-4069-9455-F0555C524C97}" name="Material Standards - protocol" dataDxfId="14"/>
-    <tableColumn id="39" xr3:uid="{9D69D833-46AC-4D69-A3FE-62512232C633}" name="Blanks &amp;_x000a_Contamination_x000a_Control" dataDxfId="13"/>
-    <tableColumn id="40" xr3:uid="{9628E9F5-3972-4FE0-9F02-83F8F9AB87B8}" name="Data Analysis_x000a_&amp; Statistics" dataDxfId="12"/>
-    <tableColumn id="41" xr3:uid="{E08A5C14-9082-4603-A2E5-0F190EA86465}" name="Reporting &amp;_x000a_Harmonization" dataDxfId="11"/>
-    <tableColumn id="42" xr3:uid="{15B782A9-BA11-42A8-8714-5859A51B9793}" name="Databases &amp;_x000a_Data Sharing" dataDxfId="10"/>
-    <tableColumn id="43" xr3:uid="{38DF8C33-36D2-431F-BB1C-E55F8D19DC14}" name="Toxicology:_x000a_Study Design &amp;_x000a_Dosimetry" dataDxfId="9"/>
-    <tableColumn id="44" xr3:uid="{D753897E-2232-42BB-B6A0-E9664869043F}" name="Toxicology:_x000a_Effects Testing_x000a_Methods" dataDxfId="8"/>
-    <tableColumn id="55" xr3:uid="{E25D3005-678F-4519-BBBF-F84B844C6386}" name="Toxicology: Reporting &amp; Harmonization" dataDxfId="7"/>
-    <tableColumn id="54" xr3:uid="{794AF906-9949-4D89-A079-01CE5E48D018}" name="Toxicology: Databases &amp; Data Sharing" dataDxfId="6"/>
-    <tableColumn id="46" xr3:uid="{3158ED12-9442-4B00-8CEC-E9D37D8F4E2D}" name="Risk_x000a_Assessment /_x000a_Risk Char." dataDxfId="5"/>
-    <tableColumn id="47" xr3:uid="{0FD00342-A9D9-478F-9383-D2F6B853A44D}" name="Key Notes" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{CEDE63B6-1DE0-4F1C-819A-19776FC8DC6E}" name="Target Receptor(s)" dataDxfId="39"/>
+    <tableColumn id="14" xr3:uid="{9A4E571D-A1F6-40DC-B704-E1294F7DAB36}" name="Definitions &amp;_x000a_Terminology" dataDxfId="38"/>
+    <tableColumn id="15" xr3:uid="{941447EA-878B-4190-B298-856AC8347372}" name="Problem Formulation_x000a_/ Framework" dataDxfId="37"/>
+    <tableColumn id="16" xr3:uid="{CB178553-686B-4C5E-97E2-8A02E5FD0D55}" name="Sampling_x000a_(Field Methods)" dataDxfId="36"/>
+    <tableColumn id="17" xr3:uid="{228CC6E5-F85A-43D4-9C0D-E113F9ACA161}" name="Matrix:_x000a_Drinking Water" dataDxfId="35"/>
+    <tableColumn id="18" xr3:uid="{B123E62B-3AC0-435F-9145-4C8127CAA77C}" name="Matrix: Surface Water" dataDxfId="34"/>
+    <tableColumn id="19" xr3:uid="{CEF38C2B-2F06-4E78-A092-E2FEB97C9F52}" name="Matrix: Surface Water - Lacustrine" dataDxfId="33"/>
+    <tableColumn id="20" xr3:uid="{3694A582-64F6-4477-A9D8-06177956C242}" name="Matrix: Surface Water - Riverine" dataDxfId="32"/>
+    <tableColumn id="21" xr3:uid="{F583F8B6-3B8E-4B25-A98F-419E5647A5EA}" name="Matrix: Surface Water - Marine" dataDxfId="31"/>
+    <tableColumn id="22" xr3:uid="{85C0E723-D5C6-4324-94BB-D0F3DCA9B995}" name="Matrix:_x000a_Wastewater" dataDxfId="30"/>
+    <tableColumn id="23" xr3:uid="{8220585C-5CF1-41AF-919C-4C99A59721F7}" name="Matrix: Groundwater" dataDxfId="29"/>
+    <tableColumn id="24" xr3:uid="{FEBA89A1-F5D0-4F0D-B25F-6FB85D7243C0}" name="Matrix: Biosolids" dataDxfId="28"/>
+    <tableColumn id="25" xr3:uid="{09AB8842-0DF4-4F69-9168-1E1EDBACD5ED}" name="Matrix:_x000a_Sediment" dataDxfId="27"/>
+    <tableColumn id="26" xr3:uid="{0B7FDDE7-15ED-49F7-85D5-EC288FFD9ABF}" name="Matrix:_x000a_Soil" dataDxfId="26"/>
+    <tableColumn id="27" xr3:uid="{5C63260E-F930-45B8-BBDD-70838E6E43F5}" name="Matrix:_x000a_Biota/Tissue" dataDxfId="25"/>
+    <tableColumn id="28" xr3:uid="{DCD27DA6-354F-4360-8C09-BD78208BA02A}" name="Matrix:_x000a_Air/Atmos." dataDxfId="24"/>
+    <tableColumn id="29" xr3:uid="{4184C4AC-BEC3-404E-ACC5-AED032740DFF}" name="Matrix:_x000a_Food/Dietary" dataDxfId="23"/>
+    <tableColumn id="30" xr3:uid="{0E8CD545-AFE9-4376-8F44-48E6F9FC2936}" name="Matrix:_x000a_Human Tissue/_x000a_Biomonitor" dataDxfId="22"/>
+    <tableColumn id="31" xr3:uid="{4FAB3A2F-40D5-4FA8-BFC4-CB409107DB63}" name="Sample Processing_x000a_/ Extraction" dataDxfId="21"/>
+    <tableColumn id="32" xr3:uid="{5E7A3CB2-36D4-4594-BFB7-9F49BAA3A2D2}" name="Sub-sampling" dataDxfId="20"/>
+    <tableColumn id="33" xr3:uid="{1555478C-CD74-4F0E-9374-B5B012702DD9}" name="Analytical_x000a_Methods (General)" dataDxfId="19"/>
+    <tableColumn id="34" xr3:uid="{5E9715CD-9A76-4D03-9048-0AF3B32A2499}" name="FTIR / IR_x000a_Spectroscopy" dataDxfId="18"/>
+    <tableColumn id="35" xr3:uid="{6EF7B799-0FBF-4A00-9379-8FEADFA4E38A}" name="Raman_x000a_Spectroscopy" dataDxfId="17"/>
+    <tableColumn id="36" xr3:uid="{9C42805B-BA1D-45C3-9788-C9FB01D3D549}" name="Py-GC-MS" dataDxfId="16"/>
+    <tableColumn id="37" xr3:uid="{8DA2DD01-42A0-4C44-AB7F-B4754280832F}" name="Imaging" dataDxfId="15"/>
+    <tableColumn id="38" xr3:uid="{BB38F2B1-716D-48CA-A962-EA86DA3F849A}" name="Material Standards - materials" dataDxfId="14"/>
+    <tableColumn id="53" xr3:uid="{2E043EA4-F707-4069-9455-F0555C524C97}" name="Material Standards - protocol" dataDxfId="13"/>
+    <tableColumn id="39" xr3:uid="{9D69D833-46AC-4D69-A3FE-62512232C633}" name="Blanks &amp;_x000a_Contamination_x000a_Control" dataDxfId="12"/>
+    <tableColumn id="40" xr3:uid="{9628E9F5-3972-4FE0-9F02-83F8F9AB87B8}" name="Data Analysis_x000a_&amp; Statistics" dataDxfId="11"/>
+    <tableColumn id="41" xr3:uid="{E08A5C14-9082-4603-A2E5-0F190EA86465}" name="Reporting &amp;_x000a_Harmonization" dataDxfId="10"/>
+    <tableColumn id="42" xr3:uid="{15B782A9-BA11-42A8-8714-5859A51B9793}" name="Databases &amp;_x000a_Data Sharing" dataDxfId="9"/>
+    <tableColumn id="43" xr3:uid="{38DF8C33-36D2-431F-BB1C-E55F8D19DC14}" name="Toxicology:_x000a_Study Design &amp;_x000a_Dosimetry" dataDxfId="8"/>
+    <tableColumn id="44" xr3:uid="{D753897E-2232-42BB-B6A0-E9664869043F}" name="Toxicology:_x000a_Effects Testing_x000a_Methods" dataDxfId="7"/>
+    <tableColumn id="55" xr3:uid="{E25D3005-678F-4519-BBBF-F84B844C6386}" name="Toxicology: Reporting &amp; Harmonization" dataDxfId="6"/>
+    <tableColumn id="54" xr3:uid="{794AF906-9949-4D89-A079-01CE5E48D018}" name="Toxicology: Databases &amp; Data Sharing" dataDxfId="5"/>
+    <tableColumn id="46" xr3:uid="{3158ED12-9442-4B00-8CEC-E9D37D8F4E2D}" name="Risk_x000a_Assessment /_x000a_Risk Char." dataDxfId="4"/>
+    <tableColumn id="47" xr3:uid="{0FD00342-A9D9-478F-9383-D2F6B853A44D}" name="Key Notes" dataDxfId="3"/>
     <tableColumn id="48" xr3:uid="{4BE1F33B-7E0D-4F32-B492-F28D43B48E54}" name="Scope"/>
     <tableColumn id="49" xr3:uid="{D2279340-23C3-4EE5-8570-F5244F0755EE}" name="Status"/>
-    <tableColumn id="50" xr3:uid="{81909305-108A-4B91-BCE6-89E889DE39A8}" name="Particle_x000a_Size Range" dataDxfId="3"/>
-    <tableColumn id="51" xr3:uid="{2AECE94C-1735-4B86-999E-F6C4105FFCFE}" name="Key Metrics /_x000a_Output" dataDxfId="2"/>
-    <tableColumn id="52" xr3:uid="{2DD3D9F5-1988-478B-BB45-CD54211D41B5}" name="Abstract" dataDxfId="1"/>
+    <tableColumn id="50" xr3:uid="{81909305-108A-4B91-BCE6-89E889DE39A8}" name="Particle_x000a_Size Range" dataDxfId="2"/>
+    <tableColumn id="51" xr3:uid="{2AECE94C-1735-4B86-999E-F6C4105FFCFE}" name="Key Metrics /_x000a_Output" dataDxfId="1"/>
+    <tableColumn id="52" xr3:uid="{2DD3D9F5-1988-478B-BB45-CD54211D41B5}" name="Abstract" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6365,31 +6376,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="66.599999999999994" hidden="1" customHeight="1">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="106" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="96"/>
+      <c r="B1" s="107"/>
       <c r="C1" s="97"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="99" t="s">
+      <c r="D1" s="107"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="109" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="98"/>
-      <c r="N1" s="101" t="s">
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="111" t="s">
         <v>38</v>
       </c>
-      <c r="O1" s="102"/>
+      <c r="O1" s="98"/>
       <c r="P1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="Q1" s="103" t="s">
+      <c r="Q1" s="112" t="s">
         <v>40</v>
       </c>
       <c r="R1" s="97"/>
@@ -6404,36 +6415,36 @@
       <c r="AA1" s="97"/>
       <c r="AB1" s="97"/>
       <c r="AC1" s="97"/>
-      <c r="AD1" s="102"/>
-      <c r="AE1" s="104" t="s">
+      <c r="AD1" s="98"/>
+      <c r="AE1" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="AF1" s="102"/>
-      <c r="AG1" s="105" t="s">
+      <c r="AF1" s="98"/>
+      <c r="AG1" s="96" t="s">
         <v>42</v>
       </c>
       <c r="AH1" s="97"/>
       <c r="AI1" s="97"/>
-      <c r="AJ1" s="102"/>
+      <c r="AJ1" s="98"/>
       <c r="AK1" s="15"/>
       <c r="AL1" s="16" t="s">
         <v>43</v>
       </c>
       <c r="AM1" s="78"/>
-      <c r="AN1" s="106" t="s">
+      <c r="AN1" s="99" t="s">
         <v>44</v>
       </c>
-      <c r="AO1" s="102"/>
-      <c r="AP1" s="107" t="s">
+      <c r="AO1" s="98"/>
+      <c r="AP1" s="100" t="s">
         <v>45</v>
       </c>
-      <c r="AQ1" s="102"/>
-      <c r="AR1" s="108" t="s">
+      <c r="AQ1" s="98"/>
+      <c r="AR1" s="101" t="s">
         <v>46</v>
       </c>
-      <c r="AS1" s="109"/>
-      <c r="AT1" s="109"/>
-      <c r="AU1" s="109"/>
+      <c r="AS1" s="102"/>
+      <c r="AT1" s="102"/>
+      <c r="AU1" s="102"/>
       <c r="AV1" s="17" t="s">
         <v>44</v>
       </c>
@@ -6442,11 +6453,11 @@
       </c>
       <c r="AX1" s="19"/>
       <c r="AY1" s="19"/>
-      <c r="AZ1" s="110" t="s">
+      <c r="AZ1" s="103" t="s">
         <v>48</v>
       </c>
-      <c r="BA1" s="111"/>
-      <c r="BB1" s="112"/>
+      <c r="BA1" s="104"/>
+      <c r="BB1" s="105"/>
     </row>
     <row r="2" spans="1:54" s="4" customFormat="1" ht="57.75" customHeight="1">
       <c r="A2" s="20" t="s">
@@ -6619,7 +6630,7 @@
       <c r="B3" s="37" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="113">
+      <c r="C3" s="37">
         <v>2009</v>
       </c>
       <c r="D3" s="37" t="s">
@@ -6717,7 +6728,7 @@
       <c r="B4" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="C4" s="113">
+      <c r="C4" s="37">
         <v>2013</v>
       </c>
       <c r="D4" s="37" t="s">
@@ -6825,7 +6836,7 @@
       <c r="B5" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="C5" s="113">
+      <c r="C5" s="37">
         <v>2015</v>
       </c>
       <c r="D5" s="37" t="s">
@@ -6929,7 +6940,7 @@
       <c r="B6" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="C6" s="113">
+      <c r="C6" s="37">
         <v>2023</v>
       </c>
       <c r="D6" s="37" t="s">
@@ -7031,7 +7042,7 @@
       <c r="B7" s="37" t="s">
         <v>141</v>
       </c>
-      <c r="C7" s="113">
+      <c r="C7" s="37">
         <v>2025</v>
       </c>
       <c r="D7" s="37" t="s">
@@ -7135,7 +7146,7 @@
       <c r="B8" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="C8" s="113">
+      <c r="C8" s="37">
         <v>2024</v>
       </c>
       <c r="D8" s="37" t="s">
@@ -7241,7 +7252,7 @@
       <c r="B9" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="C9" s="113">
+      <c r="C9" s="37">
         <v>2023</v>
       </c>
       <c r="D9" s="37" t="s">
@@ -7347,7 +7358,7 @@
       <c r="B10" s="37" t="s">
         <v>163</v>
       </c>
-      <c r="C10" s="113">
+      <c r="C10" s="37">
         <v>2021</v>
       </c>
       <c r="D10" s="37" t="s">
@@ -7441,7 +7452,7 @@
       <c r="B11" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="C11" s="113">
+      <c r="C11" s="37">
         <v>2025</v>
       </c>
       <c r="D11" s="37" t="s">
@@ -7537,7 +7548,7 @@
       <c r="B12" s="37" t="s">
         <v>180</v>
       </c>
-      <c r="C12" s="113">
+      <c r="C12" s="37">
         <v>2022</v>
       </c>
       <c r="D12" s="37" t="s">
@@ -7633,7 +7644,7 @@
       <c r="B13" s="37" t="s">
         <v>190</v>
       </c>
-      <c r="C13" s="113">
+      <c r="C13" s="37">
         <v>2025</v>
       </c>
       <c r="D13" s="37" t="s">
@@ -7729,7 +7740,7 @@
       <c r="B14" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="C14" s="113">
+      <c r="C14" s="37">
         <v>2025</v>
       </c>
       <c r="D14" s="37" t="s">
@@ -7821,7 +7832,7 @@
       <c r="B15" s="37" t="s">
         <v>202</v>
       </c>
-      <c r="C15" s="113">
+      <c r="C15" s="37">
         <v>2020</v>
       </c>
       <c r="D15" s="37" t="s">
@@ -7915,7 +7926,7 @@
       <c r="B16" s="37" t="s">
         <v>212</v>
       </c>
-      <c r="C16" s="113">
+      <c r="C16" s="37">
         <v>2011</v>
       </c>
       <c r="D16" s="37" t="s">
@@ -8003,7 +8014,7 @@
       <c r="B17" s="37" t="s">
         <v>218</v>
       </c>
-      <c r="C17" s="113">
+      <c r="C17" s="37">
         <v>2019</v>
       </c>
       <c r="D17" s="37" t="s">
@@ -8095,7 +8106,7 @@
       <c r="B18" s="37" t="s">
         <v>226</v>
       </c>
-      <c r="C18" s="113">
+      <c r="C18" s="37">
         <v>2017</v>
       </c>
       <c r="D18" s="37" t="s">
@@ -8195,7 +8206,7 @@
       <c r="B19" s="37" t="s">
         <v>237</v>
       </c>
-      <c r="C19" s="113">
+      <c r="C19" s="37">
         <v>2022</v>
       </c>
       <c r="D19" s="37" t="s">
@@ -8287,7 +8298,7 @@
       <c r="B20" s="37" t="s">
         <v>245</v>
       </c>
-      <c r="C20" s="113">
+      <c r="C20" s="37">
         <v>2023</v>
       </c>
       <c r="D20" s="37" t="s">
@@ -8383,7 +8394,7 @@
       <c r="B21" s="37" t="s">
         <v>251</v>
       </c>
-      <c r="C21" s="113">
+      <c r="C21" s="37">
         <v>2024</v>
       </c>
       <c r="D21" s="37" t="s">
@@ -8477,7 +8488,7 @@
       <c r="B22" s="37" t="s">
         <v>256</v>
       </c>
-      <c r="C22" s="113">
+      <c r="C22" s="37">
         <v>2024</v>
       </c>
       <c r="D22" s="37" t="s">
@@ -8563,7 +8574,7 @@
       <c r="B23" s="37" t="s">
         <v>261</v>
       </c>
-      <c r="C23" s="113">
+      <c r="C23" s="37">
         <v>2019</v>
       </c>
       <c r="D23" s="37" t="s">
@@ -8661,7 +8672,7 @@
       <c r="B24" s="37" t="s">
         <v>267</v>
       </c>
-      <c r="C24" s="113">
+      <c r="C24" s="37">
         <v>2022</v>
       </c>
       <c r="D24" s="37" t="s">
@@ -8755,7 +8766,7 @@
       <c r="B25" s="37" t="s">
         <v>275</v>
       </c>
-      <c r="C25" s="113">
+      <c r="C25" s="37">
         <v>2025</v>
       </c>
       <c r="D25" s="37" t="s">
@@ -8845,7 +8856,7 @@
       <c r="B26" s="37" t="s">
         <v>283</v>
       </c>
-      <c r="C26" s="113">
+      <c r="C26" s="37">
         <v>2021</v>
       </c>
       <c r="D26" s="37" t="s">
@@ -8941,7 +8952,7 @@
       <c r="B27" s="37" t="s">
         <v>290</v>
       </c>
-      <c r="C27" s="113">
+      <c r="C27" s="37">
         <v>2024</v>
       </c>
       <c r="D27" s="37" t="s">
@@ -9031,7 +9042,7 @@
       <c r="B28" s="37" t="s">
         <v>299</v>
       </c>
-      <c r="C28" s="113">
+      <c r="C28" s="37">
         <v>2020</v>
       </c>
       <c r="D28" s="37" t="s">
@@ -9127,7 +9138,7 @@
       <c r="B29" s="37" t="s">
         <v>305</v>
       </c>
-      <c r="C29" s="113">
+      <c r="C29" s="37">
         <v>2025</v>
       </c>
       <c r="D29" s="37" t="s">
@@ -9225,7 +9236,7 @@
       <c r="B30" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="C30" s="113">
+      <c r="C30" s="37">
         <v>2025</v>
       </c>
       <c r="D30" s="37" t="s">
@@ -9325,7 +9336,7 @@
       <c r="B31" s="37" t="s">
         <v>1350</v>
       </c>
-      <c r="C31" s="113">
+      <c r="C31" s="37">
         <v>2022</v>
       </c>
       <c r="D31" s="37" t="s">
@@ -9425,7 +9436,7 @@
       <c r="B32" s="37" t="s">
         <v>326</v>
       </c>
-      <c r="C32" s="113">
+      <c r="C32" s="37">
         <v>2024</v>
       </c>
       <c r="D32" s="37" t="s">
@@ -9515,7 +9526,7 @@
       <c r="B33" s="37" t="s">
         <v>333</v>
       </c>
-      <c r="C33" s="113">
+      <c r="C33" s="37">
         <v>2020</v>
       </c>
       <c r="D33" s="37" t="s">
@@ -9635,7 +9646,7 @@
       <c r="B34" s="37" t="s">
         <v>341</v>
       </c>
-      <c r="C34" s="113">
+      <c r="C34" s="37">
         <v>2020</v>
       </c>
       <c r="D34" s="37" t="s">
@@ -9753,7 +9764,7 @@
       <c r="B35" s="37" t="s">
         <v>348</v>
       </c>
-      <c r="C35" s="113">
+      <c r="C35" s="37">
         <v>2023</v>
       </c>
       <c r="D35" s="37" t="s">
@@ -9847,7 +9858,7 @@
       <c r="B36" s="37" t="s">
         <v>354</v>
       </c>
-      <c r="C36" s="113">
+      <c r="C36" s="37">
         <v>2024</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -9939,7 +9950,7 @@
       <c r="B37" s="37" t="s">
         <v>362</v>
       </c>
-      <c r="C37" s="113">
+      <c r="C37" s="37">
         <v>2019</v>
       </c>
       <c r="D37" s="37" t="s">
@@ -10047,7 +10058,7 @@
       <c r="B38" s="37" t="s">
         <v>369</v>
       </c>
-      <c r="C38" s="113">
+      <c r="C38" s="37">
         <v>2019</v>
       </c>
       <c r="D38" s="37" t="s">
@@ -10145,7 +10156,7 @@
       <c r="B39" s="37" t="s">
         <v>377</v>
       </c>
-      <c r="C39" s="113">
+      <c r="C39" s="37">
         <v>2026</v>
       </c>
       <c r="D39" s="37" t="s">
@@ -10243,7 +10254,7 @@
       <c r="B40" s="37" t="s">
         <v>385</v>
       </c>
-      <c r="C40" s="113">
+      <c r="C40" s="37">
         <v>2021</v>
       </c>
       <c r="D40" s="37" t="s">
@@ -10339,7 +10350,7 @@
       <c r="B41" s="37" t="s">
         <v>393</v>
       </c>
-      <c r="C41" s="113">
+      <c r="C41" s="37">
         <v>2020</v>
       </c>
       <c r="D41" s="37" t="s">
@@ -10439,7 +10450,7 @@
       <c r="B42" s="37" t="s">
         <v>399</v>
       </c>
-      <c r="C42" s="113">
+      <c r="C42" s="37">
         <v>2026</v>
       </c>
       <c r="D42" s="37" t="s">
@@ -10531,7 +10542,7 @@
       <c r="B43" s="37" t="s">
         <v>406</v>
       </c>
-      <c r="C43" s="113">
+      <c r="C43" s="37">
         <v>2022</v>
       </c>
       <c r="D43" s="37" t="s">
@@ -10629,7 +10640,7 @@
       <c r="B44" s="37" t="s">
         <v>413</v>
       </c>
-      <c r="C44" s="113">
+      <c r="C44" s="37">
         <v>2021</v>
       </c>
       <c r="D44" s="37" t="s">
@@ -10723,7 +10734,7 @@
       <c r="B45" s="37" t="s">
         <v>420</v>
       </c>
-      <c r="C45" s="113">
+      <c r="C45" s="37">
         <v>2022</v>
       </c>
       <c r="D45" s="37" t="s">
@@ -10815,7 +10826,7 @@
       <c r="B46" s="37" t="s">
         <v>377</v>
       </c>
-      <c r="C46" s="113">
+      <c r="C46" s="37">
         <v>2026</v>
       </c>
       <c r="D46" s="37" t="s">
@@ -10909,7 +10920,7 @@
       <c r="B47" s="37" t="s">
         <v>432</v>
       </c>
-      <c r="C47" s="113">
+      <c r="C47" s="37">
         <v>2022</v>
       </c>
       <c r="D47" s="37" t="s">
@@ -11001,7 +11012,7 @@
       <c r="B48" s="37" t="s">
         <v>439</v>
       </c>
-      <c r="C48" s="113">
+      <c r="C48" s="37">
         <v>2025</v>
       </c>
       <c r="D48" s="37" t="s">
@@ -11105,7 +11116,7 @@
       <c r="B49" s="37" t="s">
         <v>449</v>
       </c>
-      <c r="C49" s="113">
+      <c r="C49" s="37">
         <v>2022</v>
       </c>
       <c r="D49" s="37" t="s">
@@ -11199,7 +11210,7 @@
       <c r="B50" s="37" t="s">
         <v>456</v>
       </c>
-      <c r="C50" s="113">
+      <c r="C50" s="37">
         <v>2019</v>
       </c>
       <c r="D50" s="37" t="s">
@@ -11293,7 +11304,7 @@
       <c r="B51" s="37" t="s">
         <v>464</v>
       </c>
-      <c r="C51" s="113">
+      <c r="C51" s="37">
         <v>2023</v>
       </c>
       <c r="D51" s="37" t="s">
@@ -11387,7 +11398,7 @@
       <c r="B52" s="37" t="s">
         <v>473</v>
       </c>
-      <c r="C52" s="113">
+      <c r="C52" s="37">
         <v>2021</v>
       </c>
       <c r="D52" s="37" t="s">
@@ -11483,7 +11494,7 @@
       <c r="B53" s="37" t="s">
         <v>479</v>
       </c>
-      <c r="C53" s="113">
+      <c r="C53" s="37">
         <v>2023</v>
       </c>
       <c r="D53" s="37" t="s">
@@ -11593,7 +11604,7 @@
       <c r="B54" s="37" t="s">
         <v>486</v>
       </c>
-      <c r="C54" s="113">
+      <c r="C54" s="37">
         <v>2021</v>
       </c>
       <c r="D54" s="37" t="s">
@@ -11685,7 +11696,7 @@
       <c r="B55" s="37" t="s">
         <v>494</v>
       </c>
-      <c r="C55" s="113">
+      <c r="C55" s="37">
         <v>2021</v>
       </c>
       <c r="D55" s="37" t="s">
@@ -11779,7 +11790,7 @@
       <c r="B56" s="37" t="s">
         <v>501</v>
       </c>
-      <c r="C56" s="113">
+      <c r="C56" s="37">
         <v>2019</v>
       </c>
       <c r="D56" s="37" t="s">
@@ -11883,7 +11894,7 @@
       <c r="B57" s="37" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="113">
+      <c r="C57" s="37">
         <v>2015</v>
       </c>
       <c r="D57" s="37" t="s">
@@ -11979,7 +11990,7 @@
       <c r="B58" s="37" t="s">
         <v>514</v>
       </c>
-      <c r="C58" s="113">
+      <c r="C58" s="37">
         <v>2016</v>
       </c>
       <c r="D58" s="37" t="s">
@@ -12079,7 +12090,7 @@
       <c r="B59" s="37" t="s">
         <v>520</v>
       </c>
-      <c r="C59" s="113">
+      <c r="C59" s="37">
         <v>2019</v>
       </c>
       <c r="D59" s="37" t="s">
@@ -12169,7 +12180,7 @@
       <c r="B60" s="37" t="s">
         <v>525</v>
       </c>
-      <c r="C60" s="113">
+      <c r="C60" s="37">
         <v>2022</v>
       </c>
       <c r="D60" s="37" t="s">
@@ -12265,7 +12276,7 @@
       <c r="B61" s="37" t="s">
         <v>532</v>
       </c>
-      <c r="C61" s="113">
+      <c r="C61" s="37">
         <v>2015</v>
       </c>
       <c r="D61" s="37" t="s">
@@ -12359,7 +12370,7 @@
       <c r="B62" s="37" t="s">
         <v>540</v>
       </c>
-      <c r="C62" s="113">
+      <c r="C62" s="37">
         <v>2024</v>
       </c>
       <c r="D62" s="37" t="s">
@@ -12451,7 +12462,7 @@
       <c r="B63" s="37" t="s">
         <v>547</v>
       </c>
-      <c r="C63" s="113">
+      <c r="C63" s="37">
         <v>2021</v>
       </c>
       <c r="D63" s="37" t="s">
@@ -12545,7 +12556,7 @@
       <c r="B64" s="37" t="s">
         <v>554</v>
       </c>
-      <c r="C64" s="113">
+      <c r="C64" s="37">
         <v>2023</v>
       </c>
       <c r="D64" s="37" t="s">
@@ -12651,7 +12662,7 @@
       <c r="B65" s="37" t="s">
         <v>562</v>
       </c>
-      <c r="C65" s="113">
+      <c r="C65" s="37">
         <v>2020</v>
       </c>
       <c r="D65" s="37" t="s">
@@ -12747,7 +12758,7 @@
       <c r="B66" s="37" t="s">
         <v>569</v>
       </c>
-      <c r="C66" s="113">
+      <c r="C66" s="37">
         <v>2024</v>
       </c>
       <c r="D66" s="37" t="s">
@@ -12853,7 +12864,7 @@
       <c r="B67" s="37" t="s">
         <v>577</v>
       </c>
-      <c r="C67" s="113">
+      <c r="C67" s="37">
         <v>2023</v>
       </c>
       <c r="D67" s="37" t="s">
@@ -12961,7 +12972,7 @@
       <c r="B68" s="37" t="s">
         <v>583</v>
       </c>
-      <c r="C68" s="113">
+      <c r="C68" s="37">
         <v>2025</v>
       </c>
       <c r="D68" s="37" t="s">
@@ -13073,7 +13084,7 @@
       <c r="B69" s="37" t="s">
         <v>590</v>
       </c>
-      <c r="C69" s="113">
+      <c r="C69" s="37">
         <v>2026</v>
       </c>
       <c r="D69" s="37" t="s">
@@ -13171,7 +13182,7 @@
       <c r="B70" s="37" t="s">
         <v>597</v>
       </c>
-      <c r="C70" s="113">
+      <c r="C70" s="37">
         <v>2023</v>
       </c>
       <c r="D70" s="37" t="s">
@@ -13261,7 +13272,7 @@
       <c r="B71" s="58" t="s">
         <v>605</v>
       </c>
-      <c r="C71" s="114">
+      <c r="C71" s="95">
         <v>2026</v>
       </c>
       <c r="D71" s="58" t="s">
@@ -13351,7 +13362,7 @@
       <c r="B72" s="37" t="s">
         <v>613</v>
       </c>
-      <c r="C72" s="113">
+      <c r="C72" s="37">
         <v>2024</v>
       </c>
       <c r="D72" s="37" t="s">
@@ -13441,7 +13452,7 @@
       <c r="B73" s="37" t="s">
         <v>619</v>
       </c>
-      <c r="C73" s="113">
+      <c r="C73" s="37">
         <v>2024</v>
       </c>
       <c r="D73" s="37" t="s">
@@ -13533,7 +13544,7 @@
       <c r="B74" s="37" t="s">
         <v>627</v>
       </c>
-      <c r="C74" s="113">
+      <c r="C74" s="37">
         <v>2023</v>
       </c>
       <c r="D74" s="37" t="s">
@@ -13623,7 +13634,7 @@
       <c r="B75" s="37" t="s">
         <v>633</v>
       </c>
-      <c r="C75" s="113">
+      <c r="C75" s="37">
         <v>2017</v>
       </c>
       <c r="D75" s="37" t="s">
@@ -13719,7 +13730,7 @@
       <c r="B76" s="37" t="s">
         <v>641</v>
       </c>
-      <c r="C76" s="113">
+      <c r="C76" s="37">
         <v>2023</v>
       </c>
       <c r="D76" s="37" t="s">
@@ -13811,7 +13822,7 @@
       <c r="B77" s="37" t="s">
         <v>649</v>
       </c>
-      <c r="C77" s="113">
+      <c r="C77" s="37">
         <v>2023</v>
       </c>
       <c r="D77" s="37" t="s">
@@ -13905,7 +13916,7 @@
       <c r="B78" s="37" t="s">
         <v>656</v>
       </c>
-      <c r="C78" s="113">
+      <c r="C78" s="37">
         <v>2023</v>
       </c>
       <c r="D78" s="37" t="s">
@@ -13997,7 +14008,7 @@
       <c r="B79" s="37" t="s">
         <v>661</v>
       </c>
-      <c r="C79" s="113">
+      <c r="C79" s="37">
         <v>2025</v>
       </c>
       <c r="D79" s="37" t="s">
@@ -14099,7 +14110,7 @@
       <c r="B80" s="37" t="s">
         <v>666</v>
       </c>
-      <c r="C80" s="113">
+      <c r="C80" s="37">
         <v>2024</v>
       </c>
       <c r="D80" s="37" t="s">
@@ -14191,7 +14202,7 @@
       <c r="B81" s="37" t="s">
         <v>674</v>
       </c>
-      <c r="C81" s="113">
+      <c r="C81" s="37">
         <v>2019</v>
       </c>
       <c r="D81" s="37" t="s">
@@ -14283,7 +14294,7 @@
       <c r="B82" s="37" t="s">
         <v>682</v>
       </c>
-      <c r="C82" s="113">
+      <c r="C82" s="37">
         <v>2017</v>
       </c>
       <c r="D82" s="37" t="s">
@@ -14379,7 +14390,7 @@
       <c r="B83" s="58" t="s">
         <v>688</v>
       </c>
-      <c r="C83" s="114">
+      <c r="C83" s="95">
         <v>2026</v>
       </c>
       <c r="D83" s="58" t="s">
@@ -14469,7 +14480,7 @@
       <c r="B84" s="37" t="s">
         <v>694</v>
       </c>
-      <c r="C84" s="113">
+      <c r="C84" s="37">
         <v>2025</v>
       </c>
       <c r="D84" s="37" t="s">
@@ -14589,7 +14600,7 @@
       <c r="B85" s="37" t="s">
         <v>703</v>
       </c>
-      <c r="C85" s="113">
+      <c r="C85" s="37">
         <v>2023</v>
       </c>
       <c r="D85" s="37" t="s">
@@ -14679,7 +14690,7 @@
       <c r="B86" s="37" t="s">
         <v>709</v>
       </c>
-      <c r="C86" s="113">
+      <c r="C86" s="37">
         <v>2025</v>
       </c>
       <c r="D86" s="37" t="s">
@@ -14769,7 +14780,7 @@
       <c r="B87" s="37" t="s">
         <v>714</v>
       </c>
-      <c r="C87" s="113">
+      <c r="C87" s="37">
         <v>2024</v>
       </c>
       <c r="D87" s="37" t="s">
@@ -14863,7 +14874,7 @@
       <c r="B88" s="37" t="s">
         <v>722</v>
       </c>
-      <c r="C88" s="113">
+      <c r="C88" s="37">
         <v>2022</v>
       </c>
       <c r="D88" s="37" t="s">
@@ -14955,7 +14966,7 @@
       <c r="B89" s="37" t="s">
         <v>731</v>
       </c>
-      <c r="C89" s="113">
+      <c r="C89" s="37">
         <v>2019</v>
       </c>
       <c r="D89" s="37" t="s">
@@ -15055,7 +15066,7 @@
       <c r="B90" s="37" t="s">
         <v>739</v>
       </c>
-      <c r="C90" s="113">
+      <c r="C90" s="37">
         <v>2026</v>
       </c>
       <c r="D90" s="37" t="s">
@@ -15151,7 +15162,7 @@
       <c r="B91" s="58" t="s">
         <v>747</v>
       </c>
-      <c r="C91" s="114">
+      <c r="C91" s="95">
         <v>2026</v>
       </c>
       <c r="D91" s="61" t="s">
@@ -15245,7 +15256,7 @@
       <c r="B92" s="37" t="s">
         <v>753</v>
       </c>
-      <c r="C92" s="113">
+      <c r="C92" s="37">
         <v>2017</v>
       </c>
       <c r="D92" s="37" t="s">
@@ -15339,7 +15350,7 @@
       <c r="B93" s="37" t="s">
         <v>760</v>
       </c>
-      <c r="C93" s="113">
+      <c r="C93" s="37">
         <v>2022</v>
       </c>
       <c r="D93" s="37" t="s">
@@ -15439,7 +15450,7 @@
       <c r="B94" s="37" t="s">
         <v>767</v>
       </c>
-      <c r="C94" s="113">
+      <c r="C94" s="37">
         <v>2021</v>
       </c>
       <c r="D94" s="37" t="s">
@@ -15531,7 +15542,7 @@
       <c r="B95" s="37" t="s">
         <v>776</v>
       </c>
-      <c r="C95" s="113">
+      <c r="C95" s="37">
         <v>2023</v>
       </c>
       <c r="D95" s="37" t="s">
@@ -15619,7 +15630,7 @@
       <c r="B96" s="37" t="s">
         <v>783</v>
       </c>
-      <c r="C96" s="113">
+      <c r="C96" s="37">
         <v>2025</v>
       </c>
       <c r="D96" s="37" t="s">
@@ -15711,7 +15722,7 @@
       <c r="B97" s="37" t="s">
         <v>791</v>
       </c>
-      <c r="C97" s="113">
+      <c r="C97" s="37">
         <v>2025</v>
       </c>
       <c r="D97" s="37" t="s">
@@ -15811,7 +15822,7 @@
       <c r="B98" s="37" t="s">
         <v>799</v>
       </c>
-      <c r="C98" s="113">
+      <c r="C98" s="37">
         <v>2025</v>
       </c>
       <c r="D98" s="37" t="s">
@@ -15905,7 +15916,7 @@
       <c r="B99" s="37" t="s">
         <v>806</v>
       </c>
-      <c r="C99" s="113">
+      <c r="C99" s="37">
         <v>2020</v>
       </c>
       <c r="D99" s="37" t="s">
@@ -16003,7 +16014,7 @@
       <c r="B100" s="37" t="s">
         <v>814</v>
       </c>
-      <c r="C100" s="113">
+      <c r="C100" s="37">
         <v>2021</v>
       </c>
       <c r="D100" s="37" t="s">
@@ -16097,7 +16108,7 @@
       <c r="B101" s="37" t="s">
         <v>820</v>
       </c>
-      <c r="C101" s="113">
+      <c r="C101" s="37">
         <v>2022</v>
       </c>
       <c r="D101" s="37" t="s">
@@ -16193,7 +16204,7 @@
       <c r="B102" s="37" t="s">
         <v>827</v>
       </c>
-      <c r="C102" s="113">
+      <c r="C102" s="37">
         <v>2025</v>
       </c>
       <c r="D102" s="37" t="s">
@@ -16287,7 +16298,7 @@
       <c r="B103" s="37" t="s">
         <v>834</v>
       </c>
-      <c r="C103" s="113">
+      <c r="C103" s="37">
         <v>2025</v>
       </c>
       <c r="D103" s="37" t="s">
@@ -16385,7 +16396,7 @@
       <c r="B104" s="37" t="s">
         <v>841</v>
       </c>
-      <c r="C104" s="113">
+      <c r="C104" s="37">
         <v>2026</v>
       </c>
       <c r="D104" s="37" t="s">
@@ -16477,7 +16488,7 @@
       <c r="B105" s="37" t="s">
         <v>848</v>
       </c>
-      <c r="C105" s="113">
+      <c r="C105" s="37">
         <v>2021</v>
       </c>
       <c r="D105" s="37" t="s">
@@ -16567,7 +16578,7 @@
       <c r="B106" s="37" t="s">
         <v>856</v>
       </c>
-      <c r="C106" s="113">
+      <c r="C106" s="37">
         <v>2025</v>
       </c>
       <c r="D106" s="37" t="s">
@@ -16661,7 +16672,7 @@
       <c r="B107" s="37" t="s">
         <v>863</v>
       </c>
-      <c r="C107" s="113">
+      <c r="C107" s="37">
         <v>2022</v>
       </c>
       <c r="D107" s="37" t="s">
@@ -16755,7 +16766,7 @@
       <c r="B108" s="37" t="s">
         <v>870</v>
       </c>
-      <c r="C108" s="113">
+      <c r="C108" s="37">
         <v>2021</v>
       </c>
       <c r="D108" s="37" t="s">
@@ -16847,7 +16858,7 @@
       <c r="B109" s="37" t="s">
         <v>877</v>
       </c>
-      <c r="C109" s="113">
+      <c r="C109" s="37">
         <v>2021</v>
       </c>
       <c r="D109" s="37" t="s">
@@ -16955,7 +16966,7 @@
       <c r="B110" s="37" t="s">
         <v>884</v>
       </c>
-      <c r="C110" s="113">
+      <c r="C110" s="37">
         <v>2025</v>
       </c>
       <c r="D110" s="37" t="s">
@@ -17061,7 +17072,7 @@
       <c r="B111" s="37" t="s">
         <v>891</v>
       </c>
-      <c r="C111" s="113">
+      <c r="C111" s="37">
         <v>2022</v>
       </c>
       <c r="D111" s="37" t="s">
@@ -17157,7 +17168,7 @@
       <c r="B112" s="37" t="s">
         <v>898</v>
       </c>
-      <c r="C112" s="113">
+      <c r="C112" s="37">
         <v>2026</v>
       </c>
       <c r="D112" s="37" t="s">
@@ -17249,7 +17260,7 @@
       <c r="B113" s="37" t="s">
         <v>903</v>
       </c>
-      <c r="C113" s="113">
+      <c r="C113" s="37">
         <v>2022</v>
       </c>
       <c r="D113" s="37" t="s">
@@ -17351,7 +17362,7 @@
       <c r="B114" s="37" t="s">
         <v>912</v>
       </c>
-      <c r="C114" s="113">
+      <c r="C114" s="37">
         <v>2020</v>
       </c>
       <c r="D114" s="37" t="s">
@@ -17445,7 +17456,7 @@
       <c r="B115" s="37" t="s">
         <v>918</v>
       </c>
-      <c r="C115" s="113">
+      <c r="C115" s="37">
         <v>2019</v>
       </c>
       <c r="D115" s="37" t="s">
@@ -17535,7 +17546,7 @@
       <c r="B116" s="37" t="s">
         <v>924</v>
       </c>
-      <c r="C116" s="113">
+      <c r="C116" s="37">
         <v>2023</v>
       </c>
       <c r="D116" s="37" t="s">
@@ -17631,7 +17642,7 @@
       <c r="B117" s="37" t="s">
         <v>931</v>
       </c>
-      <c r="C117" s="113">
+      <c r="C117" s="37">
         <v>2025</v>
       </c>
       <c r="D117" s="37" t="s">
@@ -17755,7 +17766,7 @@
       <c r="B118" s="37" t="s">
         <v>938</v>
       </c>
-      <c r="C118" s="113">
+      <c r="C118" s="37">
         <v>2025</v>
       </c>
       <c r="D118" s="37" t="s">
@@ -17845,7 +17856,7 @@
       <c r="B119" s="37" t="s">
         <v>946</v>
       </c>
-      <c r="C119" s="113">
+      <c r="C119" s="37">
         <v>2014</v>
       </c>
       <c r="D119" s="37" t="s">
@@ -17935,7 +17946,7 @@
       <c r="B120" s="37" t="s">
         <v>953</v>
       </c>
-      <c r="C120" s="113">
+      <c r="C120" s="37">
         <v>2017</v>
       </c>
       <c r="D120" s="37" t="s">
@@ -18027,7 +18038,7 @@
       <c r="B121" s="37" t="s">
         <v>959</v>
       </c>
-      <c r="C121" s="113">
+      <c r="C121" s="37">
         <v>2020</v>
       </c>
       <c r="D121" s="37" t="s">
@@ -18115,7 +18126,7 @@
       <c r="B122" s="37" t="s">
         <v>965</v>
       </c>
-      <c r="C122" s="113">
+      <c r="C122" s="37">
         <v>2025</v>
       </c>
       <c r="D122" s="37" t="s">
@@ -18205,7 +18216,7 @@
       <c r="B123" s="37" t="s">
         <v>971</v>
       </c>
-      <c r="C123" s="113">
+      <c r="C123" s="37">
         <v>2021</v>
       </c>
       <c r="D123" s="37" t="s">
@@ -18299,7 +18310,7 @@
       <c r="B124" s="37" t="s">
         <v>979</v>
       </c>
-      <c r="C124" s="113">
+      <c r="C124" s="37">
         <v>2025</v>
       </c>
       <c r="D124" s="37" t="s">
@@ -18393,7 +18404,7 @@
       <c r="B125" s="37" t="s">
         <v>987</v>
       </c>
-      <c r="C125" s="113">
+      <c r="C125" s="37">
         <v>2007</v>
       </c>
       <c r="D125" s="37" t="s">
@@ -18483,7 +18494,7 @@
       <c r="B126" s="37" t="s">
         <v>994</v>
       </c>
-      <c r="C126" s="113">
+      <c r="C126" s="37">
         <v>2025</v>
       </c>
       <c r="D126" s="37" t="s">
@@ -18581,7 +18592,7 @@
       <c r="B127" s="37" t="s">
         <v>1001</v>
       </c>
-      <c r="C127" s="113">
+      <c r="C127" s="37">
         <v>2026</v>
       </c>
       <c r="D127" s="37" t="s">
@@ -18673,7 +18684,7 @@
       <c r="B128" s="37" t="s">
         <v>1010</v>
       </c>
-      <c r="C128" s="113">
+      <c r="C128" s="37">
         <v>2019</v>
       </c>
       <c r="D128" s="37" t="s">
@@ -18765,7 +18776,7 @@
       <c r="B129" s="37" t="s">
         <v>1014</v>
       </c>
-      <c r="C129" s="113">
+      <c r="C129" s="37">
         <v>2020</v>
       </c>
       <c r="D129" s="37" t="s">
@@ -18857,7 +18868,7 @@
       <c r="B130" s="37" t="s">
         <v>1021</v>
       </c>
-      <c r="C130" s="113">
+      <c r="C130" s="37">
         <v>2019</v>
       </c>
       <c r="D130" s="37" t="s">
@@ -18947,7 +18958,7 @@
       <c r="B131" s="37" t="s">
         <v>1028</v>
       </c>
-      <c r="C131" s="113">
+      <c r="C131" s="37">
         <v>2004</v>
       </c>
       <c r="D131" s="37" t="s">
@@ -19043,7 +19054,7 @@
       <c r="B132" s="37" t="s">
         <v>1032</v>
       </c>
-      <c r="C132" s="113">
+      <c r="C132" s="37">
         <v>2025</v>
       </c>
       <c r="D132" s="37" t="s">
@@ -19133,7 +19144,7 @@
       <c r="B133" s="37" t="s">
         <v>1040</v>
       </c>
-      <c r="C133" s="113">
+      <c r="C133" s="37">
         <v>2023</v>
       </c>
       <c r="D133" s="37" t="s">
@@ -19221,7 +19232,7 @@
       <c r="B134" s="37" t="s">
         <v>1047</v>
       </c>
-      <c r="C134" s="113">
+      <c r="C134" s="37">
         <v>2024</v>
       </c>
       <c r="D134" s="37" t="s">
@@ -19313,7 +19324,7 @@
       <c r="B135" s="37" t="s">
         <v>1055</v>
       </c>
-      <c r="C135" s="113">
+      <c r="C135" s="37">
         <v>2025</v>
       </c>
       <c r="D135" s="37" t="s">
@@ -19431,7 +19442,7 @@
       <c r="B136" s="37" t="s">
         <v>1063</v>
       </c>
-      <c r="C136" s="113">
+      <c r="C136" s="37">
         <v>2025</v>
       </c>
       <c r="D136" s="37" t="s">
@@ -19549,7 +19560,7 @@
       <c r="B137" s="37" t="s">
         <v>1070</v>
       </c>
-      <c r="C137" s="113">
+      <c r="C137" s="37">
         <v>2025</v>
       </c>
       <c r="D137" s="37" t="s">
@@ -19643,7 +19654,7 @@
       <c r="B138" s="37" t="s">
         <v>1079</v>
       </c>
-      <c r="C138" s="113">
+      <c r="C138" s="37">
         <v>2020</v>
       </c>
       <c r="D138" s="37" t="s">
@@ -19735,7 +19746,7 @@
       <c r="B139" s="37" t="s">
         <v>1086</v>
       </c>
-      <c r="C139" s="113">
+      <c r="C139" s="37">
         <v>2023</v>
       </c>
       <c r="D139" s="37" t="s">
@@ -19829,7 +19840,7 @@
       <c r="B140" s="37" t="s">
         <v>1096</v>
       </c>
-      <c r="C140" s="113">
+      <c r="C140" s="37">
         <v>2024</v>
       </c>
       <c r="D140" s="37" t="s">
@@ -19931,7 +19942,7 @@
       <c r="B141" s="37" t="s">
         <v>1103</v>
       </c>
-      <c r="C141" s="113">
+      <c r="C141" s="37">
         <v>2022</v>
       </c>
       <c r="D141" s="37" t="s">
@@ -20033,7 +20044,7 @@
       <c r="B142" s="37" t="s">
         <v>1110</v>
       </c>
-      <c r="C142" s="113">
+      <c r="C142" s="37">
         <v>2025</v>
       </c>
       <c r="D142" s="37" t="s">
@@ -20123,7 +20134,7 @@
       <c r="B143" s="37" t="s">
         <v>1115</v>
       </c>
-      <c r="C143" s="113">
+      <c r="C143" s="37">
         <v>2019</v>
       </c>
       <c r="D143" s="37" t="s">
@@ -20215,7 +20226,7 @@
       <c r="B144" s="37" t="s">
         <v>1120</v>
       </c>
-      <c r="C144" s="113">
+      <c r="C144" s="37">
         <v>2024</v>
       </c>
       <c r="D144" s="37" t="s">
@@ -20313,7 +20324,7 @@
       <c r="B145" s="37" t="s">
         <v>1126</v>
       </c>
-      <c r="C145" s="113">
+      <c r="C145" s="37">
         <v>2023</v>
       </c>
       <c r="D145" s="37" t="s">
@@ -20405,7 +20416,7 @@
       <c r="B146" s="37" t="s">
         <v>1131</v>
       </c>
-      <c r="C146" s="113">
+      <c r="C146" s="37">
         <v>2021</v>
       </c>
       <c r="D146" s="37" t="s">
@@ -20497,7 +20508,7 @@
       <c r="B147" s="37" t="s">
         <v>1137</v>
       </c>
-      <c r="C147" s="113">
+      <c r="C147" s="37">
         <v>2022</v>
       </c>
       <c r="D147" s="37" t="s">
@@ -20587,7 +20598,7 @@
       <c r="B148" s="37" t="s">
         <v>1143</v>
       </c>
-      <c r="C148" s="113">
+      <c r="C148" s="37">
         <v>2014</v>
       </c>
       <c r="D148" s="37" t="s">
@@ -20675,7 +20686,7 @@
       <c r="B149" s="37" t="s">
         <v>1150</v>
       </c>
-      <c r="C149" s="113">
+      <c r="C149" s="37">
         <v>2022</v>
       </c>
       <c r="D149" s="37" t="s">
@@ -20767,7 +20778,7 @@
       <c r="B150" s="37" t="s">
         <v>1156</v>
       </c>
-      <c r="C150" s="113">
+      <c r="C150" s="37">
         <v>2024</v>
       </c>
       <c r="D150" s="37" t="s">
@@ -20857,7 +20868,7 @@
       <c r="B151" s="37" t="s">
         <v>1162</v>
       </c>
-      <c r="C151" s="113">
+      <c r="C151" s="37">
         <v>2021</v>
       </c>
       <c r="D151" s="37" t="s">
@@ -20949,7 +20960,7 @@
       <c r="B152" s="37" t="s">
         <v>1169</v>
       </c>
-      <c r="C152" s="113">
+      <c r="C152" s="37">
         <v>2020</v>
       </c>
       <c r="D152" s="37" t="s">
@@ -21043,7 +21054,7 @@
       <c r="B153" s="37" t="s">
         <v>1176</v>
       </c>
-      <c r="C153" s="113">
+      <c r="C153" s="37">
         <v>2012</v>
       </c>
       <c r="D153" s="37" t="s">
@@ -21153,7 +21164,7 @@
       <c r="B154" s="37" t="s">
         <v>1184</v>
       </c>
-      <c r="C154" s="113">
+      <c r="C154" s="37">
         <v>2020</v>
       </c>
       <c r="D154" s="37" t="s">
@@ -21241,7 +21252,7 @@
       <c r="B155" s="37" t="s">
         <v>1190</v>
       </c>
-      <c r="C155" s="113">
+      <c r="C155" s="37">
         <v>2015</v>
       </c>
       <c r="D155" s="37" t="s">
@@ -21341,7 +21352,7 @@
       <c r="B156" s="37" t="s">
         <v>1198</v>
       </c>
-      <c r="C156" s="113">
+      <c r="C156" s="37">
         <v>2019</v>
       </c>
       <c r="D156" s="37" t="s">
@@ -21445,7 +21456,7 @@
       <c r="B157" s="37" t="s">
         <v>1204</v>
       </c>
-      <c r="C157" s="113">
+      <c r="C157" s="37">
         <v>2026</v>
       </c>
       <c r="D157" s="37" t="s">
@@ -21539,7 +21550,7 @@
       <c r="B158" s="37" t="s">
         <v>1212</v>
       </c>
-      <c r="C158" s="113">
+      <c r="C158" s="37">
         <v>2019</v>
       </c>
       <c r="D158" s="37" t="s">
@@ -21631,7 +21642,7 @@
       <c r="B159" s="37" t="s">
         <v>1219</v>
       </c>
-      <c r="C159" s="113">
+      <c r="C159" s="37">
         <v>2020</v>
       </c>
       <c r="D159" s="37" t="s">
@@ -21733,7 +21744,7 @@
       <c r="B160" s="37" t="s">
         <v>1226</v>
       </c>
-      <c r="C160" s="113">
+      <c r="C160" s="37">
         <v>2024</v>
       </c>
       <c r="D160" s="37" t="s">
@@ -21823,7 +21834,7 @@
       <c r="B161" s="37" t="s">
         <v>1233</v>
       </c>
-      <c r="C161" s="113">
+      <c r="C161" s="37">
         <v>2025</v>
       </c>
       <c r="D161" s="37" t="s">
@@ -21917,7 +21928,7 @@
       <c r="B162" s="37" t="s">
         <v>1240</v>
       </c>
-      <c r="C162" s="115">
+      <c r="C162" s="41">
         <v>2025</v>
       </c>
       <c r="D162" s="37" t="s">
@@ -22015,7 +22026,7 @@
       <c r="B163" s="37" t="s">
         <v>1246</v>
       </c>
-      <c r="C163" s="113">
+      <c r="C163" s="37">
         <v>2025</v>
       </c>
       <c r="D163" s="37" t="s">
@@ -22107,7 +22118,7 @@
       <c r="B164" s="37" t="s">
         <v>1252</v>
       </c>
-      <c r="C164" s="113">
+      <c r="C164" s="37">
         <v>2025</v>
       </c>
       <c r="D164" s="37" t="s">
@@ -22197,7 +22208,7 @@
       <c r="B165" s="37" t="s">
         <v>1260</v>
       </c>
-      <c r="C165" s="113">
+      <c r="C165" s="37">
         <v>2023</v>
       </c>
       <c r="D165" s="37" t="s">
@@ -22287,7 +22298,7 @@
       <c r="B166" s="37" t="s">
         <v>1266</v>
       </c>
-      <c r="C166" s="113">
+      <c r="C166" s="37">
         <v>1975</v>
       </c>
       <c r="D166" s="37" t="s">
@@ -22377,7 +22388,7 @@
       <c r="B167" s="37" t="s">
         <v>1273</v>
       </c>
-      <c r="C167" s="113">
+      <c r="C167" s="37">
         <v>2024</v>
       </c>
       <c r="D167" s="37" t="s">
@@ -22473,7 +22484,7 @@
       <c r="B168" s="63" t="s">
         <v>1276</v>
       </c>
-      <c r="C168" s="116">
+      <c r="C168" s="63">
         <v>2016</v>
       </c>
       <c r="D168" s="63" t="s">
@@ -22571,7 +22582,7 @@
       <c r="B169" s="63" t="s">
         <v>1286</v>
       </c>
-      <c r="C169" s="116">
+      <c r="C169" s="63">
         <v>2019</v>
       </c>
       <c r="D169" s="63" t="s">
@@ -22661,7 +22672,7 @@
       <c r="B170" s="63" t="s">
         <v>1293</v>
       </c>
-      <c r="C170" s="116">
+      <c r="C170" s="63">
         <v>2024</v>
       </c>
       <c r="D170" s="63" t="s">
@@ -22779,7 +22790,7 @@
       <c r="B171" s="37" t="s">
         <v>1298</v>
       </c>
-      <c r="C171" s="117">
+      <c r="C171">
         <v>2022</v>
       </c>
       <c r="D171" s="3" t="s">
@@ -22844,7 +22855,7 @@
       <c r="B172" s="3" t="s">
         <v>1303</v>
       </c>
-      <c r="C172" s="117">
+      <c r="C172">
         <v>2023</v>
       </c>
       <c r="D172" s="3" t="s">
@@ -22906,7 +22917,7 @@
       <c r="B173" s="3" t="s">
         <v>1309</v>
       </c>
-      <c r="C173" s="117">
+      <c r="C173">
         <v>2025</v>
       </c>
       <c r="D173" s="10" t="s">
@@ -22983,7 +22994,7 @@
       <c r="B174" s="3" t="s">
         <v>1314</v>
       </c>
-      <c r="C174" s="117">
+      <c r="C174">
         <v>2024</v>
       </c>
       <c r="D174" s="3" t="s">
@@ -23039,7 +23050,7 @@
       <c r="B175" s="3" t="s">
         <v>1319</v>
       </c>
-      <c r="C175" s="117">
+      <c r="C175">
         <v>2023</v>
       </c>
       <c r="D175" s="10" t="s">
@@ -23096,7 +23107,7 @@
       <c r="B176" s="37" t="s">
         <v>1351</v>
       </c>
-      <c r="C176" s="118">
+      <c r="C176" s="83">
         <v>2022</v>
       </c>
       <c r="D176" s="87" t="s">
@@ -23196,7 +23207,7 @@
       <c r="B177" s="3" t="s">
         <v>1364</v>
       </c>
-      <c r="C177" s="118">
+      <c r="C177" s="83">
         <v>2023</v>
       </c>
       <c r="D177" s="3" t="s">
@@ -23286,7 +23297,7 @@
       <c r="B178" s="3" t="s">
         <v>1372</v>
       </c>
-      <c r="C178" s="118">
+      <c r="C178" s="83">
         <v>2024</v>
       </c>
       <c r="D178" s="3" t="s">
@@ -23376,7 +23387,7 @@
       <c r="B179" s="3" t="s">
         <v>1376</v>
       </c>
-      <c r="C179" s="118">
+      <c r="C179" s="83">
         <v>2024</v>
       </c>
       <c r="D179" s="3" t="s">
@@ -23462,7 +23473,7 @@
       <c r="B180" s="3" t="s">
         <v>1381</v>
       </c>
-      <c r="C180" s="118">
+      <c r="C180" s="83">
         <v>2026</v>
       </c>
       <c r="D180" s="3" t="s">
@@ -23552,7 +23563,7 @@
       <c r="B181" s="3" t="s">
         <v>1391</v>
       </c>
-      <c r="C181" s="118">
+      <c r="C181" s="83">
         <v>2026</v>
       </c>
       <c r="D181" s="3" t="s">
@@ -23642,7 +23653,7 @@
       <c r="B182" s="3" t="s">
         <v>1396</v>
       </c>
-      <c r="C182" s="118">
+      <c r="C182" s="83">
         <v>2023</v>
       </c>
       <c r="D182" s="3" t="s">
@@ -23758,7 +23769,7 @@
       <c r="B183" s="3" t="s">
         <v>1403</v>
       </c>
-      <c r="C183" s="118">
+      <c r="C183" s="83">
         <v>2021</v>
       </c>
       <c r="D183" s="3" t="s">
@@ -23870,7 +23881,7 @@
       <c r="B184" s="3" t="s">
         <v>1415</v>
       </c>
-      <c r="C184" s="118">
+      <c r="C184" s="83">
         <v>2023</v>
       </c>
       <c r="D184" s="3" t="s">
@@ -23960,7 +23971,7 @@
       <c r="B185" s="3" t="s">
         <v>1414</v>
       </c>
-      <c r="C185" s="118">
+      <c r="C185" s="83">
         <v>2026</v>
       </c>
       <c r="D185" s="3" t="s">
@@ -24056,7 +24067,7 @@
       <c r="B186" t="s">
         <v>1437</v>
       </c>
-      <c r="C186" s="117">
+      <c r="C186">
         <v>2025</v>
       </c>
       <c r="D186" t="s">
@@ -24175,7 +24186,7 @@
       <c r="B187" t="s">
         <v>1436</v>
       </c>
-      <c r="C187" s="117">
+      <c r="C187">
         <v>2026</v>
       </c>
       <c r="D187" t="s">
@@ -24278,7 +24289,7 @@
       <c r="B188" s="3" t="s">
         <v>1439</v>
       </c>
-      <c r="C188" s="118">
+      <c r="C188" s="83">
         <v>2026</v>
       </c>
       <c r="D188" s="3" t="s">
@@ -24362,8 +24373,104 @@
       </c>
     </row>
     <row r="189" spans="1:54" ht="14.3" customHeight="1">
-      <c r="A189" s="70"/>
-      <c r="AW189" s="10"/>
+      <c r="A189" s="70">
+        <v>188</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C189" s="114">
+        <v>2026</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>1445</v>
+      </c>
+      <c r="E189" s="89" t="s">
+        <v>1446</v>
+      </c>
+      <c r="F189" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="G189" s="90" t="s">
+        <v>117</v>
+      </c>
+      <c r="H189" s="49" t="s">
+        <v>329</v>
+      </c>
+      <c r="I189" s="77" t="s">
+        <v>240</v>
+      </c>
+      <c r="J189" s="81"/>
+      <c r="K189" s="91" t="s">
+        <v>1447</v>
+      </c>
+      <c r="L189" s="83" t="s">
+        <v>1399</v>
+      </c>
+      <c r="M189" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="N189" s="82"/>
+      <c r="O189" s="82"/>
+      <c r="P189" s="82">
+        <v>3</v>
+      </c>
+      <c r="Q189" s="82"/>
+      <c r="R189" s="82">
+        <v>3</v>
+      </c>
+      <c r="S189" s="82">
+        <v>3</v>
+      </c>
+      <c r="T189" s="82">
+        <v>3</v>
+      </c>
+      <c r="U189" s="82">
+        <v>3</v>
+      </c>
+      <c r="V189" s="82"/>
+      <c r="W189" s="82"/>
+      <c r="X189" s="82"/>
+      <c r="Y189" s="82">
+        <v>3</v>
+      </c>
+      <c r="Z189" s="82"/>
+      <c r="AA189" s="82"/>
+      <c r="AB189" s="82"/>
+      <c r="AC189" s="82"/>
+      <c r="AD189" s="82"/>
+      <c r="AE189" s="82"/>
+      <c r="AF189" s="82"/>
+      <c r="AG189" s="82"/>
+      <c r="AH189" s="82"/>
+      <c r="AI189" s="82"/>
+      <c r="AJ189" s="82"/>
+      <c r="AK189" s="82"/>
+      <c r="AL189" s="82"/>
+      <c r="AM189" s="82"/>
+      <c r="AN189" s="82"/>
+      <c r="AO189" s="67"/>
+      <c r="AP189" s="82"/>
+      <c r="AQ189" s="82"/>
+      <c r="AR189" s="82"/>
+      <c r="AS189" s="82"/>
+      <c r="AT189" s="67"/>
+      <c r="AU189" s="82"/>
+      <c r="AV189" s="82"/>
+      <c r="AW189" s="10" t="s">
+        <v>1450</v>
+      </c>
+      <c r="AX189" s="83"/>
+      <c r="AY189" s="83"/>
+      <c r="AZ189" s="10" t="s">
+        <v>1393</v>
+      </c>
+      <c r="BA189" s="45" t="s">
+        <v>1449</v>
+      </c>
+      <c r="BB189" s="10" t="s">
+        <v>1448</v>
+      </c>
     </row>
     <row r="190" spans="1:54" ht="14.3" customHeight="1">
       <c r="A190" s="70"/>
@@ -27680,16 +27787,16 @@
     <row r="1018" spans="1:49" ht="14.3" customHeight="1"/>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="F1:M1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="Q1:AD1"/>
+    <mergeCell ref="AE1:AF1"/>
     <mergeCell ref="AG1:AJ1"/>
     <mergeCell ref="AN1:AO1"/>
     <mergeCell ref="AP1:AQ1"/>
     <mergeCell ref="AR1:AU1"/>
     <mergeCell ref="AZ1:BB1"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="F1:M1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="Q1:AD1"/>
-    <mergeCell ref="AE1:AF1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E144" r:id="rId1" xr:uid="{A81C656A-0A99-4267-9649-0EEFD2B27222}"/>
@@ -27702,10 +27809,11 @@
     <hyperlink ref="E184" r:id="rId8" display="https://doi.org/10.1016/j.ocecoaman.2023.106771" xr:uid="{544CA07B-2E2A-4DBC-9CC6-55FE9D10C148}"/>
     <hyperlink ref="E185" r:id="rId9" xr:uid="{9D95C0B9-0AF7-4B80-8A81-ABCD934682EF}"/>
     <hyperlink ref="E188" r:id="rId10" tooltip="DOI URL" xr:uid="{71E22F72-0CF3-4154-834D-5AA603563583}"/>
+    <hyperlink ref="E189" r:id="rId11" xr:uid="{C96102E8-A232-4FB7-86C2-1DF66DEBB549}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId11"/>
+    <tablePart r:id="rId12"/>
   </tableParts>
 </worksheet>
 </file>

--- a/methods_navigator/data/crosswalk.xlsx
+++ b/methods_navigator/data/crosswalk.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Scott.Coffin\Documents\Claude\Projects\Quality Manuscript\methods_navigator\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F54853E3-F5AB-4777-BF53-063D8924D940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE424CC-2518-4B98-8B1D-EEBEBC6DAC37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25974" yWindow="-4008" windowWidth="34995" windowHeight="19060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Crosswalk Table" sheetId="1" r:id="rId1"/>
     <sheet name="Reviewer" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Crosswalk Table'!$A$2:$BB$189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Crosswalk Table'!$A$2:$BB$190</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2667" uniqueCount="1451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2681" uniqueCount="1457">
   <si>
     <t>Reviewer Name</t>
   </si>
@@ -4596,6 +4596,24 @@
   </si>
   <si>
     <t>Comprehensive review up to August 2024 with harmonized recommendations on where, when, and what to sample in rivers and transitional zones.</t>
+  </si>
+  <si>
+    <t>https://pubs.acs.org/doi/full/10.1021/acs.est.5c18024</t>
+  </si>
+  <si>
+    <t>Murphy et al. 2026</t>
+  </si>
+  <si>
+    <t>Better Data, Better Outcomes: Unified Macroplastic Ingestion Reporting Methods to Inform Risk Assessment</t>
+  </si>
+  <si>
+    <t>Macroplastic</t>
+  </si>
+  <si>
+    <t>Addressing the impacts of plastic pollution, particularly plastic ingestion, on wildlife and ecosystems has become a priority for decision-makers developing management strategies. As nations design national action plans, the need for science-based targets to guide management objectives is increasingly urgent. Despite decades of evidence showing plastic ingestion in more than 1,500 species, our understanding of how ingestion affects organisms, populations, and ecosystems remains limited. Ecological risk assessments, which estimate the likelihood that a stressor will cause adverse effects at various biological levels, offer a pathway for identifying environmental thresholds. However, for macroplastic ingestion─an exposure pathway that cannot be ethically or feasibly studied in the laboratory─harmonized, large-scale environmental datasets are essential. Existing frameworks for reporting plastic ingestion are well suited for characterizing exposure in marine species, yet researchers often do not document observed harm in ways that support risk assessments. Here, we present a framework for collecting and reporting data on plastic ingestion in wildlife that better captures effects relevant to macroplastic risk assessment. Our framework builds on established ingestion protocols and introduces new approaches for measuring and reporting acute wildlife mortality and injuries attributable to plastic ingestion. Implementing this framework will continue to support long-term monitoring efforts, while improving our understanding of lethal and sublethal ingestion thresholds.</t>
+  </si>
+  <si>
+    <t>Reporting guidelines for plastic ingestion by wildlife.</t>
   </si>
 </sst>
 </file>
@@ -5404,14 +5422,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -5433,30 +5475,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
@@ -5978,8 +5996,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D7F74609-08FF-44E4-8D38-7B6CD8B94E02}" name="Table2" displayName="Table2" ref="A2:BB189" totalsRowShown="0" headerRowBorderDxfId="51">
-  <autoFilter ref="A2:BB189" xr:uid="{D7F74609-08FF-44E4-8D38-7B6CD8B94E02}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D7F74609-08FF-44E4-8D38-7B6CD8B94E02}" name="Table2" displayName="Table2" ref="A2:BB190" totalsRowShown="0" headerRowBorderDxfId="51">
+  <autoFilter ref="A2:BB190" xr:uid="{D7F74609-08FF-44E4-8D38-7B6CD8B94E02}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:BB176">
     <sortCondition ref="A2:A176"/>
   </sortState>
@@ -6376,75 +6394,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="66.599999999999994" hidden="1" customHeight="1">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="96" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="109" t="s">
+      <c r="B1" s="97"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="100" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
-      <c r="J1" s="110"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="111" t="s">
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="99"/>
+      <c r="N1" s="102" t="s">
         <v>38</v>
       </c>
-      <c r="O1" s="98"/>
+      <c r="O1" s="103"/>
       <c r="P1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="Q1" s="112" t="s">
+      <c r="Q1" s="104" t="s">
         <v>40</v>
       </c>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="97"/>
-      <c r="Y1" s="97"/>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="97"/>
-      <c r="AC1" s="97"/>
-      <c r="AD1" s="98"/>
-      <c r="AE1" s="113" t="s">
+      <c r="R1" s="98"/>
+      <c r="S1" s="98"/>
+      <c r="T1" s="98"/>
+      <c r="U1" s="98"/>
+      <c r="V1" s="98"/>
+      <c r="W1" s="98"/>
+      <c r="X1" s="98"/>
+      <c r="Y1" s="98"/>
+      <c r="Z1" s="98"/>
+      <c r="AA1" s="98"/>
+      <c r="AB1" s="98"/>
+      <c r="AC1" s="98"/>
+      <c r="AD1" s="103"/>
+      <c r="AE1" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="AF1" s="98"/>
-      <c r="AG1" s="96" t="s">
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="106" t="s">
         <v>42</v>
       </c>
-      <c r="AH1" s="97"/>
-      <c r="AI1" s="97"/>
-      <c r="AJ1" s="98"/>
+      <c r="AH1" s="98"/>
+      <c r="AI1" s="98"/>
+      <c r="AJ1" s="103"/>
       <c r="AK1" s="15"/>
       <c r="AL1" s="16" t="s">
         <v>43</v>
       </c>
       <c r="AM1" s="78"/>
-      <c r="AN1" s="99" t="s">
+      <c r="AN1" s="107" t="s">
         <v>44</v>
       </c>
-      <c r="AO1" s="98"/>
-      <c r="AP1" s="100" t="s">
+      <c r="AO1" s="103"/>
+      <c r="AP1" s="108" t="s">
         <v>45</v>
       </c>
-      <c r="AQ1" s="98"/>
-      <c r="AR1" s="101" t="s">
+      <c r="AQ1" s="103"/>
+      <c r="AR1" s="109" t="s">
         <v>46</v>
       </c>
-      <c r="AS1" s="102"/>
-      <c r="AT1" s="102"/>
-      <c r="AU1" s="102"/>
+      <c r="AS1" s="110"/>
+      <c r="AT1" s="110"/>
+      <c r="AU1" s="110"/>
       <c r="AV1" s="17" t="s">
         <v>44</v>
       </c>
@@ -6453,11 +6471,11 @@
       </c>
       <c r="AX1" s="19"/>
       <c r="AY1" s="19"/>
-      <c r="AZ1" s="103" t="s">
+      <c r="AZ1" s="111" t="s">
         <v>48</v>
       </c>
-      <c r="BA1" s="104"/>
-      <c r="BB1" s="105"/>
+      <c r="BA1" s="112"/>
+      <c r="BB1" s="113"/>
     </row>
     <row r="2" spans="1:54" s="4" customFormat="1" ht="57.75" customHeight="1">
       <c r="A2" s="20" t="s">
@@ -24379,7 +24397,7 @@
       <c r="B189" s="3" t="s">
         <v>1444</v>
       </c>
-      <c r="C189" s="114">
+      <c r="C189" s="83">
         <v>2026</v>
       </c>
       <c r="D189" s="3" t="s">
@@ -24473,8 +24491,100 @@
       </c>
     </row>
     <row r="190" spans="1:54" ht="14.3" customHeight="1">
-      <c r="A190" s="70"/>
-      <c r="AW190" s="10"/>
+      <c r="A190" s="70">
+        <v>189</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C190" s="114">
+        <v>2026</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E190" s="89" t="s">
+        <v>1451</v>
+      </c>
+      <c r="F190" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="G190" s="90" t="s">
+        <v>117</v>
+      </c>
+      <c r="H190" s="49" t="s">
+        <v>329</v>
+      </c>
+      <c r="I190" s="77" t="s">
+        <v>240</v>
+      </c>
+      <c r="J190" s="81"/>
+      <c r="K190" s="42" t="s">
+        <v>1229</v>
+      </c>
+      <c r="L190" s="83" t="s">
+        <v>1454</v>
+      </c>
+      <c r="M190" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="N190" s="82"/>
+      <c r="O190" s="82"/>
+      <c r="P190" s="82">
+        <v>3</v>
+      </c>
+      <c r="Q190" s="82"/>
+      <c r="R190" s="82"/>
+      <c r="S190" s="82"/>
+      <c r="T190" s="82"/>
+      <c r="U190" s="82"/>
+      <c r="V190" s="82"/>
+      <c r="W190" s="82"/>
+      <c r="X190" s="82"/>
+      <c r="Y190" s="82"/>
+      <c r="Z190" s="82"/>
+      <c r="AA190" s="82">
+        <v>3</v>
+      </c>
+      <c r="AB190" s="82"/>
+      <c r="AC190" s="82"/>
+      <c r="AD190" s="82"/>
+      <c r="AE190" s="82">
+        <v>3</v>
+      </c>
+      <c r="AF190" s="82"/>
+      <c r="AG190" s="82"/>
+      <c r="AH190" s="82"/>
+      <c r="AI190" s="82"/>
+      <c r="AJ190" s="82"/>
+      <c r="AK190" s="82"/>
+      <c r="AL190" s="82"/>
+      <c r="AM190" s="82"/>
+      <c r="AN190" s="82"/>
+      <c r="AO190" s="67"/>
+      <c r="AP190" s="82">
+        <v>3</v>
+      </c>
+      <c r="AQ190" s="82"/>
+      <c r="AR190" s="82"/>
+      <c r="AS190" s="82"/>
+      <c r="AT190" s="67"/>
+      <c r="AU190" s="82"/>
+      <c r="AV190" s="82"/>
+      <c r="AW190" s="10" t="s">
+        <v>1456</v>
+      </c>
+      <c r="AX190" s="83"/>
+      <c r="AY190" s="83"/>
+      <c r="AZ190" s="10" t="s">
+        <v>1386</v>
+      </c>
+      <c r="BA190" s="45" t="s">
+        <v>1449</v>
+      </c>
+      <c r="BB190" s="10" t="s">
+        <v>1455</v>
+      </c>
     </row>
     <row r="191" spans="1:54" ht="14.3" customHeight="1">
       <c r="A191" s="70"/>
@@ -27787,16 +27897,16 @@
     <row r="1018" spans="1:49" ht="14.3" customHeight="1"/>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AG1:AJ1"/>
+    <mergeCell ref="AN1:AO1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AR1:AU1"/>
+    <mergeCell ref="AZ1:BB1"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="F1:M1"/>
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="Q1:AD1"/>
     <mergeCell ref="AE1:AF1"/>
-    <mergeCell ref="AG1:AJ1"/>
-    <mergeCell ref="AN1:AO1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AR1:AU1"/>
-    <mergeCell ref="AZ1:BB1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E144" r:id="rId1" xr:uid="{A81C656A-0A99-4267-9649-0EEFD2B27222}"/>
@@ -27810,10 +27920,11 @@
     <hyperlink ref="E185" r:id="rId9" xr:uid="{9D95C0B9-0AF7-4B80-8A81-ABCD934682EF}"/>
     <hyperlink ref="E188" r:id="rId10" tooltip="DOI URL" xr:uid="{71E22F72-0CF3-4154-834D-5AA603563583}"/>
     <hyperlink ref="E189" r:id="rId11" xr:uid="{C96102E8-A232-4FB7-86C2-1DF66DEBB549}"/>
+    <hyperlink ref="E190" r:id="rId12" xr:uid="{8048047A-11A2-4914-AA30-CADB42BA1A40}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId12"/>
+    <tablePart r:id="rId13"/>
   </tableParts>
 </worksheet>
 </file>
